--- a/04_extract_results/ai_review_batches/batch_004.xlsx
+++ b/04_extract_results/ai_review_batches/batch_004.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:N151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,25 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>previous_sentence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>next_sentence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai_relevant</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>relevance_level</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>sentence_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rule_matched_pathways</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>matched_keywords</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ethanol_specific</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>oxygenate_related</t>
         </is>
@@ -486,19 +516,47 @@
           <t>S0451</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The coverage of intermediate (θ ) is a function of CO COx representsalower*Hcoverage.Theexperimentaldatarevealthatthe adsorptionenergy(E )andlocalCO concentration([CO]).Tovary COx x x increaseofhydrophobicitywillleadtoanincreasing*COcoverageand theintermediate(*CO/*H)coverage,changingthelocalconcentration adecreasing*Hcoverage(Fig.5b). ofreactant(CO)atthecatalystlayerratherthan*CO/*Hadsorption x Further,thereactionpathwaysoncatalystsurfaceswithdifferent energyis,therefore,apromisingapproach.Comparedwiththeclaswettability can be understood (Fig. 5c).</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>At equilibrium, the surface sicalmodulationoftheactivesite,thenoveltyofourmethodisthatthe coverageoftheintermediate(*CO,*H)isdirectlyproportionaltothe CO RRiscompletelycontrolledbykinetics(masstransport)through 2 concentration of reactants (CO , H O).</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>For example, the relevance controllableinterfacialwettability(SupplementaryFigs.39,40).Thus, 2 2 betweenthesurfacecoverageofadsorbed*CO (θ ,x=1or2)onthe the hydrophobic modification can enhance the gas transport and x COx catalystandthelocalconcentrationofCO ([CO]),whichisgivenas increasethesurficialadsorptionofCO ,resultingintheincreaseof x x 2 Eq.(1)5,42 *CO intermediateunderbias.Moreover,thehydrophobicsurfacemay 2 further trap the produced CO, which can increase the local conθ COx =θ× (cid:1) CO x (cid:3) ×e(cid:1)EC R O T x ð1Þ c c e in n g tr t a h t e io C n – o C f c C o O up a l n in d g t t h o e C c 2 o + v p e r r o a d ge uc o t f s5 * ,2 C 0, O 48. i A n n te o r t m he e r d k ia e t y e, in th te u r s m e e n d h ia an te - H C/HO H C 4 2 5 2 )%( ycneiciffe ciadaraF 1.7 1.6 1.5 1.4 1.3 1.2 1.1 1.0 CA: 131° CA: 156° 100 CH 2 4 80 CHOH 2 5 C 2+ 60 40 20 0 CA: 43° (Cu) (Cu-12C) (Cu-18C) )V(OC*foegnaregatloV )mμ(ecnatsid yecaD Article https://doi.org/10.1038/s41467-023-39351-2 a CA:43o CA:131o CA:156o Wettability b -2 R=0.95 R=0.18 0 R=0.24 *CO 2 4 6 *H 8 10 12 CA: 43° (Cu) (Cu-12C) (Cu-18C) *CO/*H c CO CO CO 2 2 2 CO C 2 H 4 C 2 H 4 HO HO HO 2 2 2 H 2 C 2 H 5 OH C 2 H 5 OH d Selectivity Fig.5|Illustrationoftheroleofcontrollablewettabilityonthereaction distance(*H)(denotedasR,V/μm)isadoptedtorepresentthe*CO/*Hratio. pathwaysofethyleneandethanol.aSchematicsofinterfacialcontactstatesofCu cSchematicsofthereactionpathwaysandproductformationonCu,Cu-12C,Cu- (CA:43°,liquid-gascontact),Cu-12C(CA:131°,gas–liquid–solidcontact),andCu18Cwithdifferentwettability(blue:liquid,white:gas).dThevarietyofproduct 18C(CA:156°,gas-solidcontact).Thewhiteandbluepartsintheschematics selectivitywithdifferentinterfacialwettability.ThereactionpathwayofC2product representgasandliquid,respectively.bCorrelationbetweeninterfacialwettability isjointlydeterminedby*COcoverageand*Hcoverage.TheFaradaicefficiencies and*COand*H.Voltagerangesfromin-situATR-SEIRASspectraanddecaydistowardethanolandC ofupto53.7%and86.1%,respectively.Theillustrations 2+ tancesfromCLSMareusedtocompare*COand*Hcoverage,respectively,at showthatthekinetic-controlled*CO/*Hratioderivedfromtheinterfacialcontact differentinterfacialwettability.Withtheincreaseofhydrophobicity,*COcoverage stateaffectstheethyleneandethanolpathways.CA:contactangle. increaseswhile*Hcoveragedecreases.Theratioofvoltagerange(*CO)overdecay NatureCommunications|( 2023)1 4:3575 7</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -520,19 +578,47 @@
           <t>S0452</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>In a conventional carbon monoxide reductionreaction(CORR)testinKOH,weshowthat,intheabsenceofacetaldehydeinsolution,anoptimumratioofn-propanol/ ethylene formation is found at intermediate CO partial pressure.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>From these observations, we can assume that the highest npropanol formation rate from CO RR is reached when a suitable ratio of CO and acetaldehyde intermediates is adsorbed.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>An 2 optimum ratio was also found for n-propanol/ethanol formation but with a clear decrease in the formation rate for ethanol at this optimum, while the n-propanol formation rate was the highest.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -554,19 +640,47 @@
           <t>S0453</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ACS Catalysis pubs.acs.org/acscatalysis ResearchArticle reduction with 20% of FE at −8.5 mA cm−2.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Enhancement of conditions, a maximum n-propanol formation rate is reached the activity toward n-propanol is also commonly achieved when ethanol formation is minimal, suggesting that ethanol using alloying strategies.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>A Pd−Cu foam (Pd Cu ) electrode and n-propanol share methylcarbonyl as an intermediate. 9 91 was shown to form n-propanol with 13.7% of FE, corresponding to a current density of −1.15 mA cm−2 at 2.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -588,19 +702,47 @@
           <t>S0454</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Enhancement of conditions, a maximum n-propanol formation rate is reached the activity toward n-propanol is also commonly achieved when ethanol formation is minimal, suggesting that ethanol using alloying strategies.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>A Pd−Cu foam (Pd Cu ) electrode and n-propanol share methylcarbonyl as an intermediate. 9 91 was shown to form n-propanol with 13.7% of FE, corresponding to a current density of −1.15 mA cm−2 at 2.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>METHODS −0.65 V vs RHE.12 More recently, Wang et al. showed that 2.1.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -622,19 +764,47 @@
           <t>S0455</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Electrochemistry.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>All electrochemical experiments adsorbed methylcarbonyl (dehydrogenated acetaldehyde) werecarriedoutinthehomemadePEEKH-cell(total15mL) intermediate (H 3 C−CO*).22,23 It has also been suggested in a three-electrode configuration.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>A dimensionally stable that n-propanol is formed via CO* trimerization (CO−CO− anode (DSA,Magneto SpecialAnodes)was usedas acounter CO),24 which is then further reduced to the alcohol.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -656,19 +826,47 @@
           <t>S0456</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All electrochemical experiments adsorbed methylcarbonyl (dehydrogenated acetaldehyde) werecarriedoutinthehomemadePEEKH-cell(total15mL) intermediate (H 3 C−CO*).22,23 It has also been suggested in a three-electrode configuration.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>A dimensionally stable that n-propanol is formed via CO* trimerization (CO−CO− anode (DSA,Magneto SpecialAnodes)was usedas acounter CO),24 which is then further reduced to the alcohol.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Even if electrode.TheDSAwasseparatedfromtheworkingelectrode both pathways would occur simultaneously, they would (Cu, as prepared before) using a Nafion 117 membrane depend differently on local concentrations.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -690,19 +888,47 @@
           <t>S0457</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A myriad of studies have ered the last common precursor in the ethylene and ethanol routes, 2 2+ focused on understanding the C–C coupling mechanism, and although although experimental confirmation is still missing2,7.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>In fact, glyoxal some consensus has been reached, the dependence of these paths on and glycolaldehyde reduce to acetaldehyde, ethanol and ethylene the particular material history is yet to be confirmed5,6.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Several couglycol only on polycrystalline copper16–18, suggesting an exclusive pling pathways have been proposed7,8, suggesting adsorbed CO (*CO) ethanol-selective route via *OCHCH.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -724,19 +950,47 @@
           <t>S0458</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Energy Environ.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Sci. 13, 4301 (2020). calculations for metals and semiconductors using a plane-wave 16.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Schouten, K.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -758,19 +1012,47 @@
           <t>S0459</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Such hypothesis has been recently challenged by 2 The proposed OCHCH -mediated ethanol pathway suggests an mechanistic studies of CO reduction50; thus, competing RDSs may 2 updated reaction scheme for CORR towards C products (Fig. 7). exist depending on the catalyst morphology.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>If formed, the CO–CO(H) 2 2+ Ethylene and ethanol formations are pH-independent on the RHE species is characterized by either a single or double C–C bond7 scale5.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Thus, according to the state of the art2,7, CO–CO dimeriza- (Supplementary Table 18) and acts as a selectivity switch between tion, which involves a single electron transfer, is assumed to be the C and C products (C selectivity-determining step 1, SDS1). 1 2+ 2+ Nature Energy | Volume 9 | December 2024 | 1485–1496 1491 )Ve( E∆ HCHCO* 2 )Ve( E∆ O* pota a b –2.4 –2.7 0 1 2 3 4 5 6 0 1 2 3 4 5 6 ∑(∆d/d)N –1 (%) ∑(∆d/d)N –1 (%) Cu–Cu Cu–Cu c d 40 Ethylene 20 0 10 0 Ethanol Ethylene 20 Distorted domains Undercoordinated High strain sites Deep s sates 0 0 5 10 15 20 25 )%( ycneiciffe ciadaraF Ethanol Methane Faradaic efficiency of CO (%) Fig. 6 | Morphological descriptors for COR to C products. a,b, Correlation Faradaic efficiency versus CO Faradaic efficiency.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -792,27 +1074,51 @@
           <t>S0460</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>The red-shift of the *CO peaks with increase in 1 1 higherP2/P1ratiosobservedoverAgCuNWsuggesthigher*COcovappliedcathodicpotentialisduetotheStarkeffectarisingfromthe erages on the AgCu NW surface, which shall benefit formation of decreasedresonancefrequenciesinnegativeelectricfields38.Inparti- *COCOintermediatesforethyleneproduction35,55.Besides,theRaman cular, the absorption peak of the *COCO intermediate at 1561cm−1 peaksat704,1072and1556cm−1observedacrossthepotentialrange appeared at −0.4V vs.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>RHE and reached the maximum intensity at from−0.6to−1.4Vvs.RHEcanbeassignedtoin-planeνCO -,adsorbed −1.2Vvs.RHE,whichispositivelycorrelatedwiththeethyleneFaradaic 2 carbonatespecies(νCO 2-)andν CO −,respectively53.OverAgCuNW, efficiency, suggesting that*COCO iscrucial for ethylene generation 3 as 2 1 acharacteristicpeakat537cm−1thatcanbeassignedto*OHspecies, overAgCuNW(Fig.4d,f)12.Additionally,aclearabsorptionpeakcould wasobservedat−0.6Vvs.RHE,whichgraduallygrewwithincreasing beidentifiedat1400cm−1thatcanbeassignedtotheadsorbed*COOH NatureCommunications|( 2024)1 5:10247 5</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>P1:*COCO; P1:COCO</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -834,19 +1140,47 @@
           <t>S0461</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>All chemical ments were carried out in a SPECS PHOIBOS 100 analyzer using reagents were used as received without any further purification. monochromaticX-raysourceofAlKαradiation(1486.6eV),andthe Deionizedwater(18.2MΩ)wasusedinallexperimentalprocesses. overall spectrum resolution is Ag 3d , &lt;0.5eV FWHM at 5/2 20kcps@UHV.Theworkingelectrode(1×1cm2),consistingofcarbon PreparationofCunanowires(CuNW) paperwithdrop-castedcatalyst,wasimmersedinCO -saturated0.1M 2 Uniform Cu NW were synthesized following a previously reported KHCO solution.Toavoidsurfaceoxidationofthecatalyst,theH-type 3 methodwithslightimprovements62.Inatypicalsynthesis,firstly,glucellwasplacedinagloveboxfortheCO RR.AfterCO RR,thesample 2 2 cose (250mg, 1.4mmol), CuCl ·2H O (117mg, 0.7mmol), and hexwasrapidlytransferredthroughachamberwithultrahighvacuumfor 2 2 adecylamine(900mg,3.8mmol)weredissolvedin50mLofdeionized XPStesting.Quasiin-situXPSspectrawerecollectedatopen-circuit water under vigorous stirring at 50oC for 12h.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Subsequently, the condition(OCV,immersedinKHCO electrolyte),−0.7and−1.2Vvs. 3 homogeneoussolutionwaskeptinawaterbathat75oCandstirredfor RHE,respectively. 24huntilthesolutionturnedbrown.Afterwards,theabovesolution wastransferredintoa150mLpressurebottleandheatedat120°Cfor OperandoXASmeasurements 24h.Aftercoolingtoroomtemperature,theproductswerecollected X-ray Absorption Spectroscopy (XAS) and operando XAS measureby centrifugation at 16099.2 (×g) for 5min.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The obtained reddishmentswereperformedinthetotal-fluorescenceyield(TFY)modeat brownCuNWwaswashedwithhotdeionizedwater(60°C),ethanol, room temperature.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,19 +1202,47 @@
           <t>S0462</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>The FEs of all products tested in the flow-cell were well reproduced in the MEA electrolyzer (Fig. 2i and Supplementary Figs. 51-52, summarized in Supplementary Table 9).</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>At a cell voltage of -3.47 V, Co -Sub-CuS catalystsS achieved a FE of 78.7%, a 0.050 EtOH S partial current density of ≈ 550.9 mA cm-2 for EtOH, and aE full-cell energy efficiency (EE ) full‑cell R of ≈ 26.1% for EtOH (Supplementary Fig. 53), compaPred with previously reported electrocatalysts N for selective ethanol production in an MEA electrolyzer, exhibited competitive electrocatalytic I E performance (Supplementary Table 10).</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The FE /FE ratio at different cell voltages was also C2 CO L C evaluated (Supplementary Fig. 54), with a ratio of ≈ 13 at -3.47 V, indicating the high C-C coupling I T orientation capability.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -902,19 +1264,47 @@
           <t>S0463</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>19</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>A peak at 1540 cm-1, indicative of *OCCO species, was detected on CuS and Co -Sur-CuS, a 0.050 key intermediate in traditional C-C symmetric coupling using surface-adsorbed *CO42,49,50.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Stronger bands at 1335 cm-1 and 1117 cm-1 were detected on Co -Sub-CuS, which are 0.050 attributed to *OC H 38,49,51-53, a key intermediate in EtOH production (Fig. 3a).</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In contrast, only 2 5 weak *OC H signals were detected, or none at all, on Co -Sur-CuS and CuS, respectively 2 5 0.050</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -936,19 +1326,47 @@
           <t>S0464</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The difference in reactivity is mainly A due to interactions between the catalysts and the *CHC*OH and *CHCHO* intermediates.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>To explore the bonding characteristics at the interface, the projected crystal orbital Hamilton population (-pCOHP) analysis was conducted.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>On Vs-CuS, *CHC*OH is adsorbed at the Cu and 1 Cu sites with the anti-bonding orbitals below the Fermi level (Fig. 4e), suggesting that the 2 *CHC*OH intermediate is stabilized by Vs-CuS.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -970,19 +1388,47 @@
           <t>S0465</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>To explore the bonding characteristics at the interface, the projected crystal orbital Hamilton population (-pCOHP) analysis was conducted.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>On Vs-CuS, *CHC*OH is adsorbed at the Cu and 1 Cu sites with the anti-bonding orbitals below the Fermi level (Fig. 4e), suggesting that the 2 *CHC*OH intermediate is stabilized by Vs-CuS.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In contrast, on Co-Sub-CuS, the C-Cu bond 1 shows anti-bonding states crossing the Fermi level, indicating electronic instability of the *CHC*OH adsorbed on Co-Sub-CuS.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1004,19 +1450,43 @@
           <t>S0466</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>(c) Energy profiles for the *CO + *COH → OCCOH* on VsCuS and Co-Sub-CuS.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Initial state (IS), transition state (TS) and final state (FS) are depicted in the</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1038,19 +1508,47 @@
           <t>S0467</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Density of states were calculated and weighted by the respective Hamilton matrix elements using the Local-Orbital Basis Suite Towards Electronic-Structure Reconstruction software package (LOBSTER)57.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>The anti-bonding and bonding interactions were analyzed based on the projected crystal orbital Hamilton population (-pCOHP) method.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Changes in reaction energy for the competing pathways leading to C products were calculated. 2 We calculated the activation barriers for asymmetric coupling of *CO and *COH to form *OCCOH using the dimer method implemented in the CP2K code with the Quickstep module58.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1072,19 +1570,47 @@
           <t>S0468</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Among these C products, ethanol (EtOH) is 2 particularly promising due to its high energy density (26.8 MJ/kg) and ease of transport 3-7.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>As is well known, Cu-based catalysts are among the most efficienSt and promising catalysts for S electrochemically reducing CO to ethanol8-11.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>However, cuErrent documentation on the directional 2 R selectivity for EtOH on Cu-based electrocatalystsP remains sparse, primarily owing to the N notoriously sluggish C-C coupling kinetics and the unsettled bifurcation pathway involving a I series of selective determining intermed E iates (SDI)12-15.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,19 +1632,47 @@
           <t>S0469</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>41</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>(c) Energy profiles for the *CO + *COH → OCCOH* on VsCuS and Co-Sub-CuS.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Initial state (IS), transition state (TS) and final state (FS) are depicted in the insets.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>(d) Energy profiles for the reduction of *CHCO.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1140,19 +1694,47 @@
           <t>S0470</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>In this regard, the binding strength of O atoms in the 2 *CHCHO* on the surface of Cu-based electrocatalysts could seSrve as a crucial descriptor for S evaluating the bifurcation potential between C H and EEtOH formation.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>In current Cu-based 2 4 R catalysts system, however, the experimental identPification and induction of *CHCHO* from N *CHCO have not been reported, primarily due to the uncontrollable binding of O atoms and the I uncertainty surrounding the adsorption fo E rm of the SDI8-11,16,17.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Therefore, there is a pressing need L C to develop a rational and versatile catalyst design strategy to direct the branching SDI pathway I T toward EtOH, focusingR on controlling the adsorption configuration of oxygen-binding A intermediates (*CHCHO*).</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1174,19 +1756,43 @@
           <t>S0471</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS promising approach to creating specific electronic states, thereby enabling precise regulation of surface oxophilicity and inducing the branching SDI, *CHCHO*.</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In this work, we developed a facile and scalable strategy to synthesize subsurface Co-doped CuS catalysts (Co-Sub-CuS) featuring abundant sulfur vacancies (V ) and surface-subsurface S electron interactions, enabling the directional selectivity of CO electroreduction to EtOH through 2 the branching pathway from *CHCO to *CHCHO* following promoted C-C coupling.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1208,19 +1814,47 @@
           <t>S0472</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>As a sharp comparison, the FE was significantly 2 C2H5OH Therefore,theGibbsfreeenergy(ΔG)oftheC–Ccouplingstepcordecreased to less than 40% after 5h reaction in a constant static respondingtoformthekeyOC**COintermediatewascalculated,where electrolysis(Fig.6b).Bycarryingouttheasymmetricpulseelectrolysis, thevalueof ΔGonCu(100)-CAwas0.51eV,significantlylowerthan thedecayrateofFE decreaseddramatically(Fig.6c).Also,the C2H5OH that on the Cu(100) (1.75eV) (Fig. 5d).</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>This illustrated that the CA XRDpatternsofCACuafterapplyingconstantandpulseelectrolysis molecule was able to enhance the *CO stability indeed, thereby processes illustrated that the valence structure of the catalyst increasingthechances ofC–Ccoupling.Itwas wellknownthatthe remained unchanged (Fig. 6d).</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Furthermore, we verified this asymgenerationofC H wasthermodynamicallymorefavorablecompared metricpulsedelectrolysisstrategyofre-enrichingCAtotheelectrode2 4 toC HOH16.AccordingtothereactionmechanismofC H orC HOH electrolyteinterfacebyNMRtechnique.ThepresenceofCAwasbarely 2 5 2 4 2 5 formation,thefurtherreactionofthe*OC H intermediatefromthe detectableintheelectrolyteafter7000stest,thentheconcentration 2 3 hydrogenationofOC**COintermediatewascrucialindeterminingthe ofCAreached0.02mMafter17000s,andfurthertheconcentrationof mechanism for the synthesis of C products, in which the direct CAreached0.05mMafter50000s(SupplementaryFig.25,Fig.6e). 2 deoxygenationof*OC H intermediateledtoC H formation,whereas Whereas when a continuous pulsed electrolysis was employed, a 2 3 2 4 theretentionofC–Obondin*OC H intermediateshiftedtowardsthe relativelylowCAconcentrationintheelectrolytewasemerged(near 2 3 synthesis of C HOH.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1242,19 +1876,47 @@
           <t>S0473</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>The coherence length of the length derived from Rietveld refinement of the XRD metallic Ag phase is on average slightly decreased after patterns.ThecoherencelengthofCuOagreeswellwiththe CORR,whichagreeswiththepartialre-dispersionofAgon 2 2 size distribution obtained by STEM analysis, although it is theCusurfaceandtheAg-richdomainslikelybeingformed slightly smaller than the mean NC edge length.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>The atomic frommultipleAgNPs. fractions of metallic Ag in the as-prepared Ag/CuO agree Quasi-in situ X-ray photoelectron spectroscopy (XPS) 2 well with the Cu/Ag composition obtained by ICP-MS measurementswereperformedtogaindeeperinsightintothe (TableS5).</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>This confirms that the majority of the added Ag surface composition and chemical state of the AgNPfrom the AgNO solution was incorporated in the AgNPs, decorated and pure CuONCs before and after 2h of 3 2 and that the initial ratios of the metal salts utilized were CORR.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1276,19 +1938,47 @@
           <t>S0474</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>The latter is in agreement with thequasi-insituXPSanalysis.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>At more negative potentials, the operando SERS data of the AgNPdecoratedCuONCsexhib2 it significant differences compared to the bare CuONCs during CORR: 2 2 1)At higher Raman shifts, a broad band of the C@O vibrations appeared at 2088cm@1 for CuONCs 2 during CORR, while for 2 Ag/CuO a shoulder at 2 2031cm@1 is more pronounced.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>This might be assignedtothemultisitebinding mechanism on the AgCu surface, where each Figure6.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1310,19 +2000,47 @@
           <t>S0475</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Theauthorsdeclarenoconflictofinterest.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Keywords: CO electroreduction · CuO· CuAgalloy · Conclusion 2 2 operandosurface-enhanced Ramanspectroscopy · operandoX-rayabsorption spectroscopy Insummary,AgNP-decoratedCuOnanocubesdisplayed 2 enhanced selectivity toward C liquid products, while the 2+ production of formate and hydrogen was suppressed.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>By [1] a)S.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1344,19 +2062,47 @@
           <t>S0476</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Our results Complete contact information is available at: demonstratethatthehydrocarbonselectivitycanbeeffectively https://pubs.acs.org/10.1021/jacs.1c03443 controlledandthatonecanswitchbetweenC andC product 1 2 formation by properly choosing the pulsing conditions.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Notes Operando spectroscopy and ex situ microscopy measurements T■he authors declare no competing financial interest. revealedthatsuchselectivitytrendscanbeassignedtodifferent factors.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The irreversible changes in the morphology of the Cu ACKNOWLEDGMENTS NCs observed after pulsed electrolysis with E an = 0.9 V were This work was funded by the Deutsche ForschungsgemeinfoundtoplayakeyroleintheenhancementoftheC 2 product schaft (DFG, German Research Foundation), project no. formation.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1378,19 +2124,47 @@
           <t>S0477</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-021-27456-5 firstlyelectrodepositedongasdiffusionlayer(GDL,Sigracet22BB,FuelCellStore) QuantificationoftheCO 2 RRproducts.Theelectrochemicaldatawererecorded usedasgasdiffusionelectrode(GDE)andthenfunctionalsolutionsweredropwhilesimultaneouslycollectingtheCORRgasproductsbyusinganautomatic 2 coatedonthecatalystside,whiletheothersideoftheGDLwascoveredwith samplerconnectedtothecathodeoutlet.Acoldtrapwasusedtocollecttheliquid polyamidetape.TheGDLwasthentapeonagraphitefoilandsubsequently,the productsbeforethesampler.Foreachappliedpotential,thegasproductswere electrodewasmountedinanoperandocellwiththegraphitefoilactingasa collectedatleastthreetimeswithpropertimeintervals.Thegasaliquotswerethen workingelectrodeandwindow.A0.5MsolutionofKHCO wasusedaselectrolyte injectedintoanonlinegaschromatograph(Agilent,MicroGC-490)equippedwith 3 fortheCORRandthecellwascontinuouslypurgedwithCO duringthemeaaTCDdetectorandMolsieve5Acolumncontinuously.Hydrogenandargon 2 2 surements.Allmeasurementswereperformedatconstantpotentialsof−1.2V, (99.9999%)wereusedasthecarriergases.Liquidproductswerequantifiedby1H −1.1V,−1.0Vand−0.9Vvs.RHE.Time-resolvedspectrawererecordedevery NMRspectroscopy(600MhzAvanceIIIBukrerwithacryorobeProdigyTCI) 30minuntilnofurtherchangeswereobservedunderCORRconditions. usingdeionizedwaterwith0.1%(w/w)ofDSS(Sodiumtrimethylsilylpropane2 DataalignmentandnormalizationoftheX-rayabsorptionnear-edgestructure sulfonate)likeinternalstandardforthequantificationoftheethanolandformate.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>(XANES)spectrawereconductedbyusingtheAthenasoftware.TofittheCu An1Dsequencewatersuppressionwithexcitationsculptingwithgradients(zgesgp) K-edgeextendedX-rayabsorptionfinestructure(EXAFS)spectraχ(k)k2,therange wasusedfortheacquisition(Numberofscan=32,DelayD1=30s).Owingtothe ofparameterRinR-spacefromR =1ÅuptoR =2.1Åwasusedforthe liquidproductcrossover,theFEvaluesoftheliquidproductswerecalculatedbased min max freshlypreparedcatalysts,whileR =1.0ÅtoR =3.0Åwereusedforthe onthetotalamountoftheproductscollectedontheanodeandcathodesides reductivecatalysts.Thek-rangefro m m in 3.0Å−1to10 m .0 ax Å−1withak-weightingof1, duringthesameperiod. 2,and3wereappliedintheFouriertransforms.Allfittingparametersincludingthe c C o u o – r C di u na p t a i t o h n s, n a u s m w b e e ll rs as N t , h i e nt c e o r r a r t e o c m tio ic n d s i t s o ta t n h c e es ph R o , t d o i e s l o e r c d tr e o r n fa r c e t f o e r r s en σ2 ce fo e r n C er u g – ie O sΔ an E d 0 M St E ab A ili e t l y ec m tro e l a y s z u er re w m a e s n o t p s e i r n at t e h d e a M ta EA con co st n a fi nt gu v r o a lt t a io ge n. o F f o − r 4 t . h 5 e 5 s V tab w i i l t i h ty c t o e n st t , in th u e ous wereobtained.TheS2factorsweresetto0.831. 0 feedinginCO.Thegasproductswerecollectedatfrequenttimeintervals.TheFE 2 valueswerecalculatedfromtheaveragevalueobtainedfromthreesuccessive Computationaldetails.Alldensityfunctionaltheory(DFT)calculationswere injections.Asfortheliquidproducts,thetotalliquidproductswerecollectedatthe carriedoutintheViennaAb-initioSimulationPackage(VASP)codewiththe endoftheexperiments. projectoraugmented-wave(PAW)method.Theexchange–correlationenergywas t P r e e r a d te e d w– u B si u n r g ke a – g E e r n n e z r e a r l ho gr f a ( d P i B en E t ) a f p o p rm ro a x l i i m sm a . ti A on p ( l G an G e A -w ) a w ve ith ba t s h is e withakinetic Faradaicefficiencyandenergyefficiencycalculations.TheFaradaicefficiency (FE)ofeachgasproductwascalculatedasfollows: energycutoffof500eVwaschosentoexpandtheelectronicwavefunctions.To i a n 5 ve l s a t y ig e a rs te o t f h C e u po ( s 1 s 1 ib 1) le s b la i b nd ( i 7 n .7 g 3 m 86 od Å es × b 7 e . t 7 w 3 e 8 e 6 n Å fu ), n i c n ti w on h a ic l h m t o h l e ec t u w la o r b a o n t d to c m ata la ly y s e t r s s , FE gas ¼g i ´v´ R z T i FP 0 ´ I 1 ´100% ð3Þ werekeptfixedduringrelaxation,wasbuiltwithavacuumspaceofabout20Å.For TheFaradaicefficiency(FE)ofeachliquidpr to o t d al uctwascalculatedasfollows: thegeometricaloptimizations,allatomswerefullyrelaxedtothegroundstatewith t w h h e e c re on a v 3 er × ge 3 n × ce 1 o Γ f -c e e n n e t r e g r y ed an M d o f n o k r h ce o s rs s t e - t P ti a n c g k t s o ch 1 e . m 0× ed 10 k − -m 5e e V sh a w n a d s 0 u . s 0 e 1 d e t V o Å sa − m 1 p , le FE liquid ¼l i ´ Q z to i tal F´100% ð4Þ thefirstBrillouinzone.Tocomparethebondstrengthbetweeneachgroupof Theformationrate(R)foreachspecies(i)wascalculatedasfollows: u fu s n in c g tio th n e al fo m ll o o l w ec i u n l g ar fo a r n m d u C la u : (111),theadsorptionenergy(E ads )iscalculatedby R i ¼ 96; Q 48 to 5 ta ´ l ´ z F ´ E t i ´S ð5Þ i E ads ¼E Cu=FM (cid:2)E Cu (cid:2)E FM ð1Þ Thefull-cellenergyefficiencies(EE)wascalculatedasfollows: whereE Cu/FM ,E Cu ,andE FM denotethetotalelectronicenergiesofanadsorbed EE¼ ð1:23(cid:2)E i Þ´FE i ð6Þ system,acleanCu(111)surface,andthefreefunctionalmolecular,respectively.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>E cell whereg representsthevolumefractionofgasproducti;vrepresentsthegasflow ElectrochemicalinH-cellandMEAconfiguration.Allelectrochemicalmearateatth i eoutletinsccm;z representsthenumberofelectronsrequiredtoproduce i surementswerecarriedoutatanambienttemperatureandpressureusingaVSP onemoleculeofproducti;I representsthetotalcurrent;l representsthe total i electrochemicalstationfromBio-LogicScienceInstrumentsequippedwitha5A numberofmolesofliquidproducti;andQ representsthechargepassedwhile boosterandFRA32module.Thecellvoltagesreportedinallfigureswererecorded theliquidproductsarebeingcollected.P = tota 1 l .01×105Pa,T=273.15K,F= withoutiRcorrection.AllthepotentialsintheH-cellwereconvertedtovalueswith 96,485Cmol−1andR=8.314Jmol−1K−0 1;trepresentstheelectrolysistime(h);S referencetotheRHEusing: representsthegeometricareaoftheelectrode(cm2);E representsthe i E RHE ¼E Ag=AgCl þ0:197Vþ0:0591´pH ð2Þ t t h h e e r c m el o l d v y o n l a ta m ge ic i p n o t t w en o t - i e a l l ec (v tr e o r d su e s s R et H up E . )forCO 2 RRtospeciesiandE cell represents IntheH-cellconfiguration,Ag/AgClreferenceelectrode(3MKCl)andPtplate wereusedasareferenceandcounterelectrodes,respectively.Theelectrolyte Data availability consistedofa0.5MKHCO solution(99.9%,SigmaAldrich),whichwassaturated withalternativelyCO (≥99. 3 998,Linde)orAr(5.0,Linde).Priortoanyexperiment, Theauthorsdeclarethatalldatasupportingtheresultsofthisstudyareavailablewithin theelectrolytesolutio 2 nsweresaturatedbybubblingCO orArforatleast20min. thepaperanditsSupplementaryInformationfilesorfromthecorrespondingauthors 2 Theelectrochemicallyactivesurfacearea(ECSA)ofthedifferentcatalystswas uponreasonablerequest. determinedusingPbunderpotentialdepositioninH-cell.AnAr-saturatedsolution of100mMHClO 4 +1mMPb(ClO 4 ) 2 wasusedasanelectrolyte.Theworking Received: 11 August 2021;Accepted: 12November 2021; electrodewasheldat−0.7Vvs.Ag/AgClfor10minandthencyclicvoltammetry wasrecordedbetween−0.7and0.7Vvs.Ag/AgClat10mVs−1.Ptfoilwasusedas thecounterelectrode,whileAr(Linde,99.998%)wascontinuouslysuppliedtothe electrolyte.TheECSAvaluesforCuandAgwerecalculatedassumingthe depositionofamonolayerofPbatomsoverCuandAgsurfacewithaconversion factorof310and260mCcm−2,respectively64.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1412,19 +2186,43 @@
           <t>S0478</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-20615-0 created by two flat (111) planes with 60° lattice orientation difTheseresultssuggestthatp-sqandcv-sqsitesareresponsiblefor ference. s-sq sites are similar to Cu(S)-[n(111)×(100)] step sites generating ethylene while s-sq favors the alcohols production. where(100)stepsareintroducedto(111)basalplane.Whilecc-sq Interestingly, we found that the tendency to produce ethylene and cv-sq are formed by rotation and then splicing of two (111) or alcohols can be simply predicted by the C–O bond length of planes.</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In order to explore C–C coupling more accurately, we *CH CHO.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1446,19 +2244,47 @@
           <t>S0479</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>The ethylene pathway probilize the newly formed *O after C–O cleavage.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>While on s-sq ceeds with cleavage of C–O bond while alcohols are formed by site, *O can only adsorb in adjacent triple site, resulting in the further protonation.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>On p-sq and cv-sq sites (Fig. 3a, b), the instabilityof*O,therebyfurtherhinderingtheethylenepathway cleavage of C–O bond to form C H is thermodynamic favored (Fig. 3f).</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1480,19 +2306,47 @@
           <t>S0480</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>While on s-sq ceeds with cleavage of C–O bond while alcohols are formed by site, *O can only adsorb in adjacent triple site, resulting in the further protonation.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>On p-sq and cv-sq sites (Fig. 3a, b), the instabilityof*O,therebyfurtherhinderingtheethylenepathway cleavage of C–O bond to form C H is thermodynamic favored (Fig. 3f).</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Based on the analysis above, we elucidated how the 2 4 compared to the protonation of α-C to form *CH CHO intergeometry of C–C active sites affects the bifurcation pathway, 3 mediate.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1514,19 +2368,47 @@
           <t>S0481</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" t="n">
+        <v>14</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>(c) Cathodic energy efficiency for C H OH formation (Cathodic EE ) of MoP-Im and MoP compared to state-of-the-art 2 5 C2H5OH catalytic systems.[11,12,26–33] The data shown in this figure are obtained at the maximum C H OH 2 5 formation FE of each catalyst in the literature considering no overpotential losses at the anode.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>(d) C H OH formation turnover frequency (TOF ) calculations for MoP and MoP-Im.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>(e) Stability analysis 2 5 C2H5OH of MoP-Im in eCO RR at a potential of -0.5 V.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1548,19 +2430,47 @@
           <t>S0482</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" t="n">
+        <v>16</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>the TOF for MoP is 0.185 s-1.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Since TOF values represent the intrinsic activity of C2H5OH catalytically active sites (i.e., Mo atoms), the difference in TOF values at the same applied C2H5OH potentials for MoP-Im and MoP catalysts is potentially due to the presence of the ionomer in the MoP-Im co-catalyst.[27] To realize the C H OH formation kinetic parameters of the MoP-Im and MoP catalysts, we 2 5 employed Tafel plot analysis using the potentials and partial C H OH current densities.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Our 2 5 analysis, shown in Figure S16 (section S12, Supplementary Materials), indicates nearly the same C H OH Tafel slopes for MoP-Im and MoP catalysts suggesting a similar reaction 2 5 mechanism for both catalytic systems.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1582,19 +2492,47 @@
           <t>S0483</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" t="n">
+        <v>16</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Since TOF values represent the intrinsic activity of C2H5OH catalytically active sites (i.e., Mo atoms), the difference in TOF values at the same applied C2H5OH potentials for MoP-Im and MoP catalysts is potentially due to the presence of the ionomer in the MoP-Im co-catalyst.[27] To realize the C H OH formation kinetic parameters of the MoP-Im and MoP catalysts, we 2 5 employed Tafel plot analysis using the potentials and partial C H OH current densities.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Our 2 5 analysis, shown in Figure S16 (section S12, Supplementary Materials), indicates nearly the same C H OH Tafel slopes for MoP-Im and MoP catalysts suggesting a similar reaction 2 5 mechanism for both catalytic systems.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>However, the MoP-Im co-catalyst has a C H OH 2 5 exchange current density (d ) of 325 µA that is 5.6-fold higher than that of MoP (58 µA).</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1616,19 +2554,47 @@
           <t>S0484</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>This work thus prepares the ground 2 for steering catalyst selectivity through dynamically controlled structural and chemical transformations.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>E lectrochemical energy conversion driven by renewable energy we steer the CORR selectivity of a CuO nanocube (NC)-derived 2 2 is a cost-effective, environmentally friendly route to convert catalyst.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>In particular, ethanol formation is doubled (compared with undesired substances (such as CO) into valuable chemicals that under stationary conditions) within a narrow range of pulse 2 and fuels.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1650,19 +2616,47 @@
           <t>S0485</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>E lectrochemical energy conversion driven by renewable energy we steer the CORR selectivity of a CuO nanocube (NC)-derived 2 2 is a cost-effective, environmentally friendly route to convert catalyst.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>In particular, ethanol formation is doubled (compared with undesired substances (such as CO) into valuable chemicals that under stationary conditions) within a narrow range of pulse 2 and fuels.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>A challenge for the practical application of complex elecdurations, where a balance between metallic copper and distorted trochemical processes, such as the CO reduction reaction (CORR) copper oxide species on the catalyst surface is achieved, as revealed 2 2 over copper-based catalysts, is control of selectivity1–5.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1684,27 +2678,55 @@
           <t>S0486</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>This suggests the electron transfer and partiallyreducedmolecular substrate in concertedlyproducing number in CO RR catalyzed by Hex-2Cu-2O is close to that inHER, 2 oxygenates,withhighselectivityofethanolandn-propanolthathas yielding the majority of 2e− reduction products such as H , CO or 2 beenrarelyseeninliterature.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>HCOOH (assuming the same type/number of active sites were engaged).Inthisvein,thereshouldbemoreelectrontransferinvolved Results in CO RR catalyzed by Hex-2Cu-O and Oct-2Cu, resulting in more 2 Catalystssynthesisandcharacterization deeplyreducedproductsof&gt;2e−.Inaddition,allthecompoundcataSyntheses of the bicentric copper complexes, denoted as HexlystsshowsignificantlyhigherLSVcurrentdensitythanthatoftheKB 2Cu-O, Hex-2Cu-2O and Oct-2Cu in Fig. 1a–c, respectively, are aloneinCO -saturatedelectrolyte,confirmingthatKB,asaconductive 2 based on the ring expansion of porphyrins following previous agent,doesnotaffecttheperformanceevaluationofthecatalysts. reports (Supplementary Fig. 1)22–25.</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Their chemical structures are Inthecontrolled-potentialelectrolysis(CPE)from–0.9to–1.5V confirmed by UV–Vis (Fig. 1d) and Mass spectroscopy (Supple- (vs RHE without iR correction, all potentials are referenced to this mentary Figs. 2–4), matching well with the literature results23,24 format hereafter unless specifically noted), Hex-2Cu-O produces and theoretical values.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1726,19 +2748,47 @@
           <t>S0487</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>In a previous publication35, we identified three major specific C 2+ product.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Thus, the fundamental selectivity issues of pathways for CORtowardsmethane (C 1 )and C 2(+) productson CO R on Cu is a challenge of great importance in catalysis and Cu(100).</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The COH/C-H (grey) pathway leads to C as the only 2 1 sustainableenergytechnologies.Substantialfocushasbeenmadein productwhereastheOCCOH(magenta)andCOH/OC-C(black) enhancingtheselectivityofC productsforCO R5–11. pathways both result in significant C production through a 2 2 2 A number of strategies have been developed to address the common intermediate dicarbon oxide (CCO*).</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1760,19 +2810,47 @@
           <t>S0488</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>The COH/C-H (grey) pathway leads to C as the only 2 1 sustainableenergytechnologies.Substantialfocushasbeenmadein productwhereastheOCCOH(magenta)andCOH/OC-C(black) enhancingtheselectivityofC productsforCO R5–11. pathways both result in significant C production through a 2 2 2 A number of strategies have been developed to address the common intermediate dicarbon oxide (CCO*).</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>A degree of rate challengeofregulatingC Oxy/HCselectivityforCO RonCu-based control analysis shows that the total COR rate depends on 2 2 catalysts, including facet engineering12,13, nanostructuring14,15, energies of key surface species essentially present in the reaction oxide-derivedCu(OD-Cu)6,11,16,alloying9,17,18,andrunningCO R pathwayswithaPETnumber(n,relativetoCO)oflessthantwo 2 intandem7.Specifically,directreductionofcarbonmonoxide(COR) (SupplementaryFig.3)35.Inotherwords,reactionstepslaterinn atalkalineconditionshasbeenwidelyreportedtoyieldsignificantC than CCO* only play a role in controlling the selectivity of C 2 2 Oxyspecies at more positive potentials thanCOR19.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>This strategy Oxy/HC for COR.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1794,19 +2872,47 @@
           <t>S0489</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Therefore, it is crucial to unveil at the surface orientation of the Cu catalysts.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>We find that the which step in each pathway the C–O bond breaks most easily and distinct pH effect on the C Oxy/HC selectivity stems from the consequently identify the product specificity of the different 2 selectivity-determining steps (SDSs) in each pathway having pathways. different proton-electron transfer (PET) numbers with water as the proton source.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>This insight allows us to propose two simple The CHCOH pathway.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1828,19 +2934,47 @@
           <t>S0490</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Since the C–O bond breaks easily absence of C HC products, acetylene and ethane, observed 2 through CHCOH-H protonation, the CHCOH pathway is conexperimentally may be attributed to the slower H-CCH protonasequently identified to exclusively produce C HCs.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Once the tion and CCH -H protonation steps compared to the steps 2 2 CCH* isformed, a seriesofCH x CH y+1 * intermediates(x, y&gt;0) towards ethylene, i.e.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>CCH-H and H-CCH 2 , respectively.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1862,19 +2996,43 @@
           <t>S0491</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29140-8 The OCHCH pathway.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Because OCHCH* is thermodynamically Figure3ashowsthetrendsintheoreticalCORcurrentdensities more stable than CHCOH* and CH CO*, it is typically conon Cu(100) obtained through microkinetic modeling, which are 2 sidered an inevitable intermediate in several proposed reaction directly comparable with the experimentally measured CO R (2) mechanisms of ethylene formation26,27.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1896,19 +3054,47 @@
           <t>S0492</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Despite the discrepancies in the absolute 2 reduction on Cu(100), and simultaneous C–O bond scission to magnitudes, our model accurately predicts the potentialgenerate atomic oxygen (O*) and the release of C H .</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Here we dependent variations in activity and selectivity and reproduces 2 4 observe that OCH CH * is a stable intermediate along the reacseveral key characteristics in experimental observations: 2 2 tion coordinates between two TSs, thus demonstrating the disjointed nature of the reaction OCHCH *+H ++e − → ● When compared to methane, larger shifts in onset O*+C H (g) (Supplementary Fig. 7).</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In sha 2 rp contrast to the potentials are observed for all C 2 species by varying the 2 4 pH.ThiscanbeattributedtothedifferenceinPETnumber extremely high barriers of directly producing ethylene from OCHCH *, reducing OCHCH * to either acetaldehyde or vinyl (relative to CO) for the rate-determining steps (RDSs) of 2 2 dominant C and C pathways at low overpotentials, i.e., alcohol is almost spontaneous at reducing conditions (Fig. 2g). 2 1 OCCO-Hprotonation forC andCOH-Hprotonationfor Vinyl alcohol is unstable in an aqueous solution at room tem2 perature and ultimately isomerizes to acetaldehyde36.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1930,19 +3116,47 @@
           <t>S0493</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>In sha 2 rp contrast to the potentials are observed for all C 2 species by varying the 2 4 pH.ThiscanbeattributedtothedifferenceinPETnumber extremely high barriers of directly producing ethylene from OCHCH *, reducing OCHCH * to either acetaldehyde or vinyl (relative to CO) for the rate-determining steps (RDSs) of 2 2 dominant C and C pathways at low overpotentials, i.e., alcohol is almost spontaneous at reducing conditions (Fig. 2g). 2 1 OCCO-Hprotonation forC andCOH-Hprotonationfor Vinyl alcohol is unstable in an aqueous solution at room tem2 perature and ultimately isomerizes to acetaldehyde36.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Once C 1 .Thisinsighthasbeendescribedindetailinourprevious work35. acetaldehydeisformed,ethanolhasbeenexperimentallyvalidated as the only further reduced C product22,37.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Compared to ● Ethyleneisamoreabundant C 2 product thanethanol and OCHCH *, OCH CH* and CHC 2 HOH* as two other possible acetate.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1964,19 +3178,47 @@
           <t>S0494</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Compared to ● Ethyleneisamoreabundant C 2 product thanethanol and OCHCH *, OCH CH* and CHC 2 HOH* as two other possible acetate.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>The predicted rate of ethylene relative to ethanol/ intermed 2 iates thro 2 ugh reduction of OCHCH* are demonstrated acetateonCu(100)isevenhigherthanthatexperimentally obtainedonpcCu,whichisinagreementwithobservations to be less favorable (Supplementary Fig. 8).</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The above analysis by Hori et al.12. suggeststhatthepossibleC productsfromtheOCHCHpathway 2 ● In the low-current-density kinetically-controlled region are limited to acetaldehyde and ethanol (Fig. 2d). and at pH13, the potential dependencies of ethylene, The CH CO pathway.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1998,19 +3240,47 @@
           <t>S0495</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>The above analysis by Hori et al.12. suggeststhatthepossibleC productsfromtheOCHCHpathway 2 ● In the low-current-density kinetically-controlled region are limited to acetaldehyde and ethanol (Fig. 2d). and at pH13, the potential dependencies of ethylene, The CH CO pathway.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Adsorbed CH CO* tends to detach from ethanol, and acetate are slightly different, indicated by a 2 2 steeper Tafel slope for ethylene than for ethanol and the surface and generate molecular ethenone in solution.</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Owing acetate.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2032,19 +3302,47 @@
           <t>S0496</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Stronger nucleophilicity of hydroxide anions − (OH ) than water further favors the reaction between ethenone We also note that the larger discrepancy in predicting acetate andOH − underhighalkalineconditions6,8,16.Theincorporation production at alkaline condition could be attributed to the ofsolventoxygenfromeitherwaterorOH − isalsosupportedby additional pathway of nucleophilic reaction between OH − and 18Oisotopelabelingexperiments8,16.Onceacetateisformed,the ethenone or surface carbonyl compounds such as CCO* and electrostatic repulsion between the negatively charged electrode CHCO*39.Furthermore,studiesthatattempttodetermineofthe and this anion species, will prevent the acetate from further Tafel slopes for CO R are often based on the RDS—through (2) reduction.ReducingCH 2 CO*towardacetaldehyde/ethanolisthe (cid:1) e 2 ð : n 3k þ B β T Þ ,wherek B istheBoltzmannconstant,Tthetemperature, relevant process competing with acetate formation, which, howetheelementarycharge,nthePETnumberbeforetheRDS,andβ ever, has hardly been investigated28.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Protonation of CH 2 CO* the charge-transfer coefficient of the RDS25,40—we note that the results in surface species CH CO*, OCHCH *, and CH COH*, 3 2 2 RDS approach of determining Tafel slopes is valid only for respectively, all of which tends to be further reduced to C Oxys 2 analyzing the total rate of CO/CO consumption or C /C (Supplementary Figs. 9 and 10).</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Compared to the OCHCH formation.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2066,19 +3364,47 @@
           <t>S0497</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>To further analyze the 2 formation of specific 1 C 2 pathway,theonlydifferenceliesintheabilityofCH COpathway 2 2 products derived from the same intermediate formed after the to produce acetate.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>RDS, the Tafel slope of each product consists of two individual From this we conclude, that the production of major C Oxy/ 2 components:onefromthetotalC formationandtheotherfrom HC species under CO R conditions stems from a common 2 (2) relative rates between different pathways.</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Due to the dynamic intermediateofCHCO*.TheprotonationstepsofCHCO*playa nature of the second component, one should be cautious with vitalroleindeterminingtheC productselectivity.TheCHCOH 2 corresponding Tafel analysis. pathway exclusively results in C HC, whereas the OCHCH and 2 Besidesthevariationofreactionrateswithpotential,pHisseen CH CO pathways lead to C Oxy only. 2 2 tohaveaprofoundeffectontheC Oxy/HCselectivity(Fig.3c). 2 To prevent the interference from the different PET number per Microkinetic model of COR and pH effects on C Oxy/HC 2 product molecule, we employed C 2 Oxy/HC molecular ratios selectivity.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2100,19 +3426,47 @@
           <t>S0498</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-29140-8 Fig.4OriginofthepHeffectsontheC Oxy/HCselectivityforCOR.AnalysesofDSCforaethylene,bethanol+acetaldehyde(denotedasethanol*), 2 andcaceticacid.SimilartothedegreeofratecontrolconceptualizedbyCampbelletal.60,DSCservesasapowerfultooltoquantifythemagnitudeof selectivitycontrollingbyacertainintermediateoraTS.Apositive(negative)valueofDSCindicatesthatthecorrespondingreactionintermediateorTS needstobestabilized(destabilized)inordertoenhancetheselectivity.Theboundaryvaluesof1and−1representfullselectivitycontrolbythe intermediates.OnlytheenergystateshavingsignificantcontributiontotheDSC,i.e.absolutevalueofDSC&gt;0.01,areshown.KeyintermediatesandTSs associatedwiththeCHCOH,OCHCH,andCH COpathwaysareshowninreddish,bluish,andgreenishcolors,respectively.Fromtheuppertolower panels,thepHofbulkelectrolyteincreasesfro 2 m7to13.Analyticalapproximationoflnðr r C2OxyÞasafunctionofdU RHE andeU SHE atpH7andpH13,in comparisonwiththetheoreticalresultsobtainedthroughmicrokineticmodeling.Theslope C s2H o C fthetwolegsaregivenbyEq.(1)andEq.(2),respectively. βOxycouldbeeitherβOCCH-HorβCHC-HOdependingonthedominantC Oxyformationpathway.HereβOCCH-HwasemployedforCu(100).Sourcedata 2 areprovidedasaSourceDatafile. controlled primarily by the second protonation step (CHCOHOn the right leg we have ΔGCHCOH(cid:1)H &gt;ΔGCHCO(cid:1)H, such that H m T o S r ) e at p l r o e w do o m v i e n rp an o t ten fo ti r als e ( t U hy R l H en E e &gt;− fo 0 rm .5 a V ti ) o . n Th a is t fa p c H to 1 r 3 b , ec w o h m er e e s ln r C2Oxy !</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>(cid:3) ðβOCCH(cid:1)H(cid:1)βCHCOH(cid:1)H(cid:1) a 1ÞeU RHE þð4GC a; H 0 a COH(cid:1)H(cid:1)4G a O ;0 CCH(cid:1)HÞ CHCOH-HTS exhibits a significantly higher DSC than at pH7 r C2HC k B T when U &gt;−0.4V.</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Such a shift with pH in the SDS is ð1Þ RHE analogous to the shift in the RDS for the COH pathway to whereas on the left leg we find ΔGCHCOH(cid:1)H &lt;ΔGCHCO(cid:1)H, such produce methane (Supplementary Fig. 3)35.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2134,19 +3488,47 @@
           <t>S0499</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>To overcome the above 2 2 (2) offeringadifferentinterpretationthanstudieswhereO/OHbinding challenges,ourdescriptor-basedapproachpresentsasimpleyet oroxophilicityarearguedtocontroltheC Oxy/HCselectivity31.For efficient way of deciphering the product-specific sites on Cu 2 instance, despite the comparable oxophilicity, stepped NiGa(111) surfacesanddesigningnewelectrocatalystsmoreselectivethan 5 3 possesses a significantly stronger ΔG C* than Cu(211) that leads to pristine Cu. predominant C HC formation as experimentally probed on Ni-Ga 2 catalysts43.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Cu-Ag9,18 and Cu-Zn alloys17 were found to selectively Methods catalyzeCO (2) RtoC 2 Oxyproducts,whichalsocanberationalized Adsorptionfreeenergycalculations.Reactionenergeticswerecalculatedwith through the principle of lowering the C* affinity.</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Besides the C* densityfunctionaltheory(DFT)withaperiodicplane-waveimplementationand affinity,theoxophilicityservesasasecondarydescriptorthatcanhelp ultrasoftpseudopotentialsusingtheQUANTUMESPRESSOcode46,interfaced guide the selectivity of ethanol over less reduced C Oxy products withtheAtomisticSimulationEnvironment(ASE)47.WeappliedtheBEEF-vdW 2 functional,whichprovidesareasonabledescriptionofvanderWaalsforceswhile such as acetate and acetaldehyde.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2168,19 +3550,47 @@
           <t>S0500</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" t="n">
+        <v>11</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>The above electronic interaction would decrease the electron density of Cu15,39,41,42 at a negative potential30,43,44.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>As a result, aldehyde would desorb from the catalyst surface before being further reduced to alcohols20,30,44.</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>To gain more insights into the effects of Ag on C-C coupling, Figure 3c looks at the branching point between C-C coupling to C products versus protonation to the C1 product CH .</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2202,19 +3612,47 @@
           <t>S0501</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" t="n">
+        <v>14</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>To deconvolute these possibilities, operando X-ray measurements were employed to provide structural and electronic information on the Cu-Ag interaction in the course of eCO2RR.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Considering that the most promising performance (i.e. the most promoted aldehydes/other carbonyls generation and facilitated C-C coupling) occurs on sample Cu Ag , 80 20 this alloy was used in the following synchrotron measurements.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Operando grazing incident X-ray diffraction (GIXRD) To monitor the crystal structure of the catalyst during eCO2RR, operando GIXRD was conducted.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2236,19 +3674,43 @@
           <t>S0502</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
         <is>
           <t>improved ethanol production when the Cu/Cu O composite was dispersed with trace amounts of 2 Ag31.</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The above divergencies demonstrate a yet-to-be-fully-understood mechanism of the interaction between Cu and Ag in eCO2RR, which generally falls into three aspects: i) if Cu and Ag have miscible phases, ii) if there is electronic and/or structural interaction between Cu and Ag, and if so, iii) how is the intermediate adsorption influenced and the resultant variation in selectivity.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>mechanism</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2270,19 +3732,47 @@
           <t>S0503</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" t="n">
+        <v>9</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>This is as expected given that Cu is known to have a higher H selectivity, whereas Ag 2 has a strong selectivity towards CO.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>In CuAg alloys, CO produced on Ag can also create a high local CO partial pressure at the adjacent Cu sites14,18,20, leading to a CO-enriched local environment, which facilitates the following C-C coupling and thus suppresses direct *CO hydrogenation to produce CH , as shown in Figure 4b and c.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Previous DFT calculations also 4 revealed weakened *H binding on the Cu surface as *CO coverage increases32 with experimental results validating this33.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2304,19 +3794,47 @@
           <t>S0504</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Zhao,K.&amp;Quan,X.Carbon-basedmaterialsforelectrochemical reductionofCO toC oxygenates:recentprogressandremaining 2 2+ j = i×FE alcohols ð6Þ challenges.ACSCatal.11,2076–2097(2021). alcohols S 2.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Bi,J.etal.Constructionof3Dcopper-chitosan-gasdiffusionlayer electrodeforhighlyefficientCO electrolysistoC alcohols.Nat. 2 2+ Commun.14,2823(2023).</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Densityfunctionaltheory(DFT)calculations 3.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -2338,19 +3856,47 @@
           <t>S0505</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-024-49247-4 environmental5.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Therefore, the feasible strategies are demanded to Mott–Schottky catalyst.</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Thus, the mechanism exploration of lowdevelop the architectural blueprint ofcatalysts and electrolytic syscoordinatedCu/Cu Oonstabilizing*COandoxyhydrocarbonsinter2 temsforpreservingtheoxidationstateandbolsteringtheCO permediatesissignificant. 2 formance of copper-based catalysts, including but not limited to Herein, we demonstrated a low-coordinated Cu/Cu O 2 elemental doping6, interface engineering7,8, intermediate Mott–Schottky catalyst with an enhanced rectifying interface (Cu / L confinement9, and pulse CO electrolysis (P-eCO R owing the Cu O).Thiscatalystadjuststheelectrondensitiesthroughinterfacial 2 2 2 straightforwardandreadilyadjustablemeansofmanipulatinganodic charge exchange, leveraging the difference in Cu and Cu O work 2 potentialsforfacilitatingtheformationofCuoxidespecies)10,11.Espefunctions,whichcaneffectivelyformbondsbetween*COandoxyhycially,theMott−Schottkycatalystpossessestheremarkableabilityto drocarbons under CER conditions.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2372,19 +3918,43 @@
           <t>S0506</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-024-49247-4 converted(αhν)1/nversushνfromtheUV-visspectrum,whereα,h,and electron-richstatusofoxygen-deficientCu+.However,theCu /Cu O P 2 νaretheabsorptioncoefficient,Planckconstant,andfrequencyofthe exhibitsaperfectMott−Schottkystructurewithoutanysignsofdefiphoton,respectively,andnis1/2foradirectbandgapsemiconductor cient oxygen (Fig. 3B and Supplementary Fig. 15).</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>From the Cl 2p or2foranindirectbandgapsemiconductor)33.TheTaucplotexhibitsa spectrums in Fig. 3C, the bonding energy of Cu–Cl also shifts to a well-matchedlinearfitwithn=1/2,whichisinlinewithpreviousartihigherstatewithdeeperAr+etchingduetothepresenceofsufficient cles supporting Cu O as a direct bandgap semiconductor (SuppleClandOatomsinthedepthofCu /Cu O.Thecleanrectifyinginterface 2 L 2 mentaryFig.11)36.TheE valueofCu /Cu Oiscalculatedtobe1.73eV regions of Cu /Cu O ensure smooth absorption and desorption, as g L 2 L 2 by measuring the x-axis intercept of an extrapolated line from the well as the coupling behavior of oxyhydrocarbon intermediates.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>pathway</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2406,19 +3976,47 @@
           <t>S0507</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" t="n">
+        <v>11</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Gao,J.etal.SelectiveC–Ccouplingincarbondioxideelectroreductionvia 1804867(2018). efficientspilloverofintermediatesassupportedbyoperandoRaman 64.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Hoang,T.etal.Nanoporouscopper–silveralloysbyadditive-controlled spectroscopy.J.Am.Chem.Soc.141,18704–18714(2019). electrodepositionfortheselectiveelectroreductionofCO toethyleneand 2 36.</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Jiang,S.,Klingan,K.,Pasquini,C.&amp;Dau,H.NewaspectsofoperandoRaman ethanol.J.Am.Chem.Soc.140,5791–5797(2018). spectroscopyappliedtoelectrochemicalCO reductiononCufoams.J.Chem. 65.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2440,19 +4038,47 @@
           <t>S0508</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Among a wide variety of catalysts tested for reactivity and concomitant morphological evolution under electrochemical CO reduction reaction (CO2RR), copper-based applied electrode potentials using in situ electrochemical liquid 2 materials, in particular Cu oxides, CuO , have been enjoying TEM and operando X-ray absorption spectroscopy (XAS).</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Next, x attentionthankstotheirwidechemicalselectivityforavarietyof using a new differential electrochemical mass spectrometry multi-carbon products, such as C 2+ hydrocarbons and oxyge- (DEMS) technique with millisecond resolution, we discuss prenates.Ithasbeenreportedthatover16kinds17ofproductscanbe viouslyunreportedtimeevolutionsofkineticonsetpotentialsofa formed on copper catalysts through multiple proton-coupled rangeofdifferentproductsoverthecourseofhours.Conclusions electron transfer processes. from our DEMS data challenge and refine our current mechanThe cathodic electrode potentials during the catalytic CO2RR istic understanding of the mechanistic link between CH and 4 invariably drive the chemical transformation of operating CuO ethanol (EtOH).</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Finally, we document the favorable CO2RR x catalystsintometallicCuphases.Thispromptedtheirdesignation performance of 2D CuO NS inside GDEs of commercial elecas oxide-derived copper (OD-Cu) catalysts.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2474,19 +4100,47 @@
           <t>S0509</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>S20 neither variation in the Cu-O bond length (first coordination contrasts oriented 2D CuO NS morphologies with the final Cu sphere),norinthatofCu-Cu.TheobtainedCNofCu0issmaller dendritemorphologyafter1600sat−0.8V validatingthereal than bulk fcc Cu0, indicating bulk and/or surface lattice defects RHE time studies.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>We conclude that facet-orientated CuO NS rapidly associatedwithundercoordinatedCuatoms.Thisisinagreement transformintonanoscalereactivesheetfragmentsthatslowlyrewith the in situ TEM results that suggested the formation of assemble into stable large agglomerations and tree-like Cu nano-sized Cu sheet fragments.</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Undercoordinated Cu sites dendrites at rates depending on applied potential/reaction time. formed during the CuO NS fragmentation and visualized in Dendritic structures are known to emerge in diffusion-limited Fig. 3, typically exhibit strong chemisorption that has been growth regimes48,49, typically present under convective flow associated with outstanding C-C coupling23,25. conditionsofelectrochemicalflowcells.Wethereforehypothesize dendritic structures—characterized by their unique tree-like MechanisticimplicationsfromDEMS-basedcatalyticratesand arborization with self-similar branch structure across several product onset potentials.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2508,19 +4162,47 @@
           <t>S0510</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="n">
+        <v>9</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Methods Discussion Synthesis.NanosizedCuOcatalystwithsheet-likemorphologywassynthesizedby We have studied the synthesis and CO electrocatalysis of a asurfactant-freewet-chemistryroute.Nopurificationwasperformedforchemicals 2 (001)-orientedCuOnanosheetcatalyst.Evaluatedinelectrolyzers beforeuse.CuOnanosheetswereobtainedbythermaldecompositionofpresynthesizedCu(OH) intermediate.ToprepareCu(OH) intermediate,100mgCu under industrially relevant pH neutral conditions, the CuO NS 2 2 (SO) wasdissolvedin4mLDI-water,2.5mL1MKOHsolutionwasthenadded catalysts featured unprecedented performance metrics for C H 42 2 4 dropwiseintothesolution.After15-minstirring,1mLammoniumhydroxidewas and C 2+.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>In situ and ex situ TEM studies revealed that over added.Theresultinghomogeneouslightbluesolutionwasthentransferredtoa 10–20min under potential control the CuO NS fractured and— glasspressurevessel.Thesealedvesselwasthenheatedfromroomtemperatureto presumably limited by diffusion of Cu species—aggregated into 80°Cin30minandstayedat80°Cfor12hbeforeitwascooledtoroomtembranched,dendriticCustructuresthatrepresentedthefinalstable p 12 er ,6 a 4 tu 9 r .6 e 3 .T g h a e n p d ro fu d r u th ct e s r w p e u r r e ifi p e r d ec t i w pi i t c a e te b d y b e y th e a th n a o n l o a l n , d se w pa a r t a er te . d A v ft i e a r c w e a n r t d ri s fu th g e a y tio w n er a e t catalyst morphology under flow conditions.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Operando XAS stufreezedriedandstoredaspowdersunderinertatmosphereuntiluse. dies confirmed the chemical reduction of CuO and concomitant formation of disordered and coordinatively under-saturated Cu0 over about 2h under reductive CO2RR conditions.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2542,19 +4224,43 @@
           <t>S0511</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
         <is>
           <t>ARTICLE OPEN https://doi.org/10.1038/s41467-022-29035-8 Operando Complementary Spectroscopy fi identi cation of in-situ generated metastable charge-asymmetry Cu -CuN clusters for CO 2 3 2 reduction to ethanol Xiaozhi Su 1,7, Zhuoli Jiang2,3,7, Jing Zhou4,7, Hengjie Liu 5, Danni Zhou2, Huishan Shang2, Xingming Ni6, ✉ ✉ Zheng Peng6, Fan Yang 6, Wenxing Chen 2 , Zeming Qi5, Dingsheng Wang 3 &amp; Yu Wang 1 Copper-based materials can reliably convert carbon dioxide into multi-carbon products but they suffer from poor activity and product selectivity.</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The atomic structure-activity relationship of electrocatalysts for the selectivity is controversial due to the lacking of systemic multiple dimensions for operando condition study.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2576,19 +4282,47 @@
           <t>S0512</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RHE, the intensity of 2 theintrinsicreactivemechanism.Inordertoidentifytherealistic the scattering peak extremely descended with an additional peak catalytic centers of Cu/N C, operando XAS study were at~2.4Å.ThisisatypicalscatteringfeatureoftheCu–Cubond. 0.14 employed to directly monitor its catalytic behavior.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>We first The conversion of CO -to-ethanol reaction occurred con2 collectedex-situXASdataofthefullyactivatedCu/N C.When currently.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The intensity of Cu–O/N scattering peak further des0.14 Cu/N C was soaked into the KHCO solution at open circuit cended with the increasing of the Cu–Cu bond as the potential 0.14 3 (OC), no obvious structural change was observed from the decreased.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2610,19 +4344,47 @@
           <t>S0513</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>This exposingtoair.TheXPSalteredcompletelyafterCO RRprocess comparisonverifiedthatthefreeze-quenchandoperandomethod 2 at−1.1Vvs.RHE.ThebindingenergyofCu2p 3/2 peaklocatedat access the same electrochemical state of the Cu/N 0.14 C (same 932.7eV and the kinetic energy L3M45M45 peak located at oxidation state and local structure).</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>The spectra which were 918.5eV corresponding to Cu0 36,43, indicating that catalysts measured for three times could be perfectly overlapped in wouldnotbeoxidizedinthetransferprocess.Therefore,theCu/C SupplementaryFig.25e–g.TheseresultsindicatedthatCu 2 –CuN 3 withoutN-dopinghadaCu0electronconfigurationwithhighH clusters oxidized without the applied potential was the chemical productivityandlessmulti-carbonproductivity.Thesedataagreed 2 reaction and Cu 2 –CuN 3 clusters in-situ generated material were well with the XAFS results, identifying a strong relationship truly metastable catalysts. between the structure of the catalysis and selectivity of multiOverall, Operando XAS study revealed that a transformation carbonproducts formation. from Cu/N 0.14 C to unique ultrasmall Cu n moiety and presented Hence,wecanconsequentlyconcludethattheCu–Cubondof the structure-activity relationships of this catalyst, indicating the theoperando spectroscopywas fromin-situgenerated ultrasmall in-situ generated Cu 2 –CuN 3 cluster is the optimal site for CO 2 Cu moieties, Cu , under the electrochemical conditions, where reduction to ethanol. n n=3 at −1.1V vs.</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>RHE.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2644,19 +4406,47 @@
           <t>S0514</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" t="n">
+        <v>7</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Interestingly, the Quasi-in situ XPS wasrealchemicalreaction,thefreeze-quenchapproachwasused oftheCu/CshoweddifferentchangesduringtheCO RRprocess, to freeze the redox state and local structure of the catalyst and 2 asshowninSupplementaryFig.17.ThebindingenergyoftheCu measured XAFS data at liquid helium temperatures (18K), as 2p peak for the pristine Cu/C was at 932.9eV and the kinetic showninSupplementaryFig.25a.TheX-rayedgeenergyaswell 3/2 energyL3M45M45peakslocatedat916.4eVcorrespondtotheCu as the spectral shape of the freeze-quench and operando spectra + species37,42, which may be due to the surface oxidation during do not differ significantly in Supplementary Fig. 25b–d.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>This exposingtoair.TheXPSalteredcompletelyafterCO RRprocess comparisonverifiedthatthefreeze-quenchandoperandomethod 2 at−1.1Vvs.RHE.ThebindingenergyofCu2p 3/2 peaklocatedat access the same electrochemical state of the Cu/N 0.14 C (same 932.7eV and the kinetic energy L3M45M45 peak located at oxidation state and local structure).</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The spectra which were 918.5eV corresponding to Cu0 36,43, indicating that catalysts measured for three times could be perfectly overlapped in wouldnotbeoxidizedinthetransferprocess.Therefore,theCu/C SupplementaryFig.25e–g.TheseresultsindicatedthatCu 2 –CuN 3 withoutN-dopinghadaCu0electronconfigurationwithhighH clusters oxidized without the applied potential was the chemical productivityandlessmulti-carbonproductivity.Thesedataagreed 2 reaction and Cu 2 –CuN 3 clusters in-situ generated material were well with the XAFS results, identifying a strong relationship truly metastable catalysts. between the structure of the catalysis and selectivity of multiOverall, Operando XAS study revealed that a transformation carbonproducts formation. from Cu/N 0.14 C to unique ultrasmall Cu n moiety and presented Hence,wecanconsequentlyconcludethattheCu–Cubondof the structure-activity relationships of this catalyst, indicating the theoperando spectroscopywas fromin-situgenerated ultrasmall in-situ generated Cu 2 –CuN 3 cluster is the optimal site for CO 2 Cu moieties, Cu , under the electrochemical conditions, where reduction to ethanol. n n=3 at −1.1V vs.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2678,19 +4468,47 @@
           <t>S0515</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>The CO adsorption 2 3 2 Cu–N site.TheN-dopingplayedanimportantroletoadjustthe energyforCu –CuN andCu –CuN hasbeencalculatedandthe 3 2 3 3 3 electron transfer and further charge distribution between the Cu result shown that the adsorption energy of CO for Cu –CuN 2 2 3 atoms and N-doped carbon interface. and Cu –CuN are +0.24eV and +0.18eV, respectively, 3 3 Theoretical investigations were conducted based on DFT implyingtheadsorptioncapacitiesforCu –CuN andCu –CuN 2 3 3 3 calculations to further understand the reaction mechanism of are close.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>However, the corresponding adsorption energy is the Cu–N with triangle pyramid geometry, Cu–CuN , +0.15eV (Cu –CuN ) and −0.36eV (Cu –CuN ), respectively, 3 3 2 3 3 3 Cu –CuN , and Cu –CuN in Supplementary Fig. 20c, f, g, h. indicatingtheadsorptioncapacitiesofHforCu –CuN aremuch 2 3 3 3 3 3 The supported CuN , Cu–CuN , Cu –CuN and Cu –CuN stronger than that for Cu –CuN .</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>These results shown the 3 3 2 3 3 3 2 3 models with a Cu bonding with three N atoms on N-doped adsorption processes of both CO and H at the Cu –CuN are 2 2 3 carbon nanosheets which were proposed to be the structure of non-spontaneous processes.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2712,19 +4530,47 @@
           <t>S0516</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>9</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Overall, our findings suggest a alterationFTIRspectroscopyandwereacquiredbyaveraging128timesscanwitha 4cm–1resolution,andthebackgroundspectrumswasconductedunderopenstrategy engineering the pre-catalysts to modulate the electron circuitvoltage,thevoltagerangesforconductingmeasurementswere0Vto–1.2V transfer and in-situ generate ultrasmall metal clusters anchored withanintervalof0.1V. onthesubstrateashighdispersionasymmetricsites,whichisthe key factor to facilitate the formation of asymmetric products.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>It wouldextendtothesingle-atomicsite,oxidecompositestructure, Quasi-insituXPSandAES.Quasi-insituX-rayphotoelectronspectroscopywas conductedofcatalystsdrop-castedoncarbonpaperassameasmentionedin and metal-support effect.</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>These catalysts have great potential to Electrodessection.BeforetesttheelectrolytesshouldbeCO-saturatedtoremove exhibit novel catalytic properties such as more efficient catalytic thedissolvedoxygeninthesolution.Sampleswerecondition 2 edatdifferent performance and higher selectivity compared to the single atom potentialfor30minasoneconditioningstep.Afterthatthesampleswasmovedto catalysts and oxide catalysts. theXPSvacuumchamberwithoutextraexposedtotheair.Thatwouldavoidthe airtoinfluencethecatalyststokeeptheauthenticstateundertheCORRprocess. 2 XPS(ESCALAB250X)wasmeasuredatAnalyticalInstrumentationCenter, Methods ShanghaiTechUniversity.Itwasusedtocharacterizethechemicalbonding PreparationofCu/N x Candthecomparisonsamples.Typically,100mgcopper characteroftheobtainedcatalystsusingamonochromaticof1486.6eV(AlKα phthalocyanineand1.0gdicyandiamidewerecontinuouslymixedinethanoland source).AllXPSspectrawerecorrectedbyC1speakwiththebindingenergyat entirelydried.Subsequently,thedriedmixturewaspyrolyzedfor2hintheN 284.6eV.Allofthereagentswereusedwithoutfurtherpurification. 2 atmosphereatdifferenttemperaturetoobtainaseriesofCu/NCsampleswith x differentnitrogencontent(x=0.14,0.11,0.02,correspondingpyrolysistemperatureat800°C,900°C,1000°C,respectively.xismasscontentratioofnitrogento Freeze-quenchXAS.TheCu/N 0.14 Cwaselectrodepositedonacarbonpaper carbon).Collectobtainedblackpowderafterpyrolysisanddirectlyusedforfurther electrode,whichwasanintegralpartoftheXASsampleholder.TheCu/N 0.14 Cwas characterizationsandcatalyticperformancetest.Cu/Cwaspreparedwithcopper equilibratedpotentiostaticallyfor20minat−1.1Vvs.RHE.TheCu/N 0.14 C chlorideandtrimesicacid.Thepyrolysistemperaturewas800°Candother electrodewasrapidlyfrozenbyimmersioninliquidnitrogen.Thechemical synthesisconditionswerethesameasabove. reactionisextremelyslowatlowtemperatureenvironmentandthechemicalstate ofthecatalystwaswellpreservedforXAFSdatacollectionperiods.X-ray absorptionspectraattheCuK-edgewerecollectedatbeamlineBL14W1ofthe Characterization.TEMimageswerecarriedoutbytheJEOLJEM-2100FmicroSSRFusingaLytledetectorwiththeNifilter.Themeasurementswereperformedat scope(200kV).AFMwasobtainedonSPM-960AFM.Typically,smallamountof 18Kusingacryostat(ARS).Theexcitationenergies(scanrange8779–9779eV) samplewasultrasonicallydispersedintheaqueoussolution.ForAFMmeasurewereselectedbyaSi(111)double-crystalmonochromator. ment,10μLofthecompletelydispersedsolutionwascarefullydroppedonaflat micasheet,andthenplaceditinafumehoodtoairdry.ForTEM,10μLofthe dispersedsolutionpreparedabovewasdroppedonacoppermeshwithcarbon supportfilm.EDSelementalmappingandHAADF-STEMwerecharacterizedbya Computationalmethods.DFTcalculationswereperformedwithintheframeof plane-wave-baseddensityfunctionaltheory(DFT)byVASPpackage.ThegenJEOLARM-200microscope(200kV)withaprobesphericalaberrationcorrector. eralizedgradientapproximation(GGA)inthePerdew−Burke−Ernzerhof(PBE) X-raypowderdiffraction(XRD)spectrawereobservedbyRigakuTTR-IIIXRDof CuKαradiation(λ=1.5418Å).XPSspectrawereacquiredonaPerkinElmer formalismwasadoptedtotreattheelectronexchangeandcorrelationenergy.The cut-offenergywassettobe500eV.Forstructuraloptimization,3×3×2k-points PhysicsPHI5300spectrometer57. mesheswithatheoriginalMonkhorst-Packschemewasusedandtheconvergence ofenergyandforcewere10−6eVand0.01eVÅ−1,respectively.6×6×4k-points Electrochemicalmeasurements.Electrochemicalmeasurementswereaccommesheswereusedforstaticcalculations.A20Åvacuumlayerinthez-axis plishedinagas-tightH-typecellatCHI760Eelectrochemicalworkstation directionwasaddedtoavoidtheinterfereofthelayerimagecouplingcausedbythe (ShanghaiChenhua,China).Forpreparationoftheworkingelectrode,2mgofthe periodicboundaryconditions59.Formoredetails,pleaseseeSupplementary catalystwasdissolvedin500μlsolution(including10μlNafionsolution(5wt%) Figs.20, 28, 29, 31andSupplementaryDatafile1–13.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2746,19 +4592,47 @@
           <t>S0517</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>T co h m es p e a fi re n d din w g i s th ind th ic o a s t e e t f h or at C an u 2 A O g/ N Cu Cs O ( h S e u t p e p ro le s m tru en ct t u ar r y e bimetallic catalysts for CO RR at high conversion rates is 2 unclear, which significantly 2 hinders understanding of the withalteredelectronstructureforCu 2 OwasreachedwithCu 2 O/ Ag NCs. mechanism and catalyst design3,14.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Taken together, there is a 2.3% need therefore for more efficient catalysts and an improved understandingofthemechanismforCO 2 RRtopracticallyboost Catalyst evolution under CO 2 RR.</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Given the reported evolution EtOH under commercial current densities. of Cu-based catalysts under high current CO RR36, activation 2 Here, through modifying Ag onto cubic Cu O and activating and in situ characterization was therefore conducted for Cu O/ 2 2 underCO RR,weinvestigatedderivedCuAgbimetallics(dCu O/ Ag NCs to determine the actual state of the catalyst during 2 2 2.3% Ag) with controlled morphology, phase, and composition for CO RR.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2780,19 +4654,47 @@
           <t>S0518</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" t="n">
+        <v>6</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>It was found that there is no coordinated surface and optimal oxidation of Cu in dCu O/ 2 apparent decay of activity with 6h continuous operation, in Ag are responsible for boosted EtOH selectivity.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Therefore, 2.3% which the selectivity of EtOH decreased ~6% following CO RR the CO RR intermediates chemisorbed on dCu O, dCu O/ 2 2 2 2 (Supplementary Fig. 23).</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>TEM image and XRD pattern of spent Ag , and dCu O/Au at different potentials were assessed 2.3% 2 2.3% dCu O/Ag showed that morphology and structure are via in situ attenuated total reflectance infrared absorption 2 2.3% maintained following the stability test (Supplementary Fig. 24). spectroscopy (ATR–IRAS) to determine the mechanism for Given the superior EtOH production on dCu O/Ag , it was boosted EtOH. 2 2.3% consequently assessed in a commercially relevant membrane As is shown in Fig. 5a, b and Supplementary Fig. 29, with the electrodeassembly(MEA)(SupplementaryFig.25).Itwasfound cathode potentialat −0.3V , the ATR–IRAS spectra for these RHE that there is a good, linear relationship between applied current catalysts exhibit several new peaks.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2814,19 +4716,47 @@
           <t>S0519</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" t="n">
+        <v>6</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TEM image and XRD pattern of spent Ag , and dCu O/Au at different potentials were assessed 2.3% 2 2.3% dCu O/Ag showed that morphology and structure are via in situ attenuated total reflectance infrared absorption 2 2.3% maintained following the stability test (Supplementary Fig. 24). spectroscopy (ATR–IRAS) to determine the mechanism for Given the superior EtOH production on dCu O/Ag , it was boosted EtOH. 2 2.3% consequently assessed in a commercially relevant membrane As is shown in Fig. 5a, b and Supplementary Fig. 29, with the electrodeassembly(MEA)(SupplementaryFig.25).Itwasfound cathode potentialat −0.3V , the ATR–IRAS spectra for these RHE that there is a good, linear relationship between applied current catalysts exhibit several new peaks.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>These are assigned to andvoltageintheMEA(Fig.4e).TheFEsforallproductstested corresponding intermediates based on independently reported in flow cell electrolyzer were well-reproduced in MEA (Supplestudies (Supplementary Table 4).</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In particular, there appear two mentary Fig. 26 and Fig. 4d), identifying that high current and peaks at 2044 and 1923cm −1 for dCu O/Ag , which are 2 2.3% high EtOH selectivity can be maintained under commercially associated with the atop–adsorbed * CO ( * CO ) and atop relevant conditions (Fig. 4e).</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2848,19 +4778,47 @@
           <t>S0520</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" t="n">
+        <v>7</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-31427-9 Fig.4CO RRperformancefordCu O/AgwithmodifiedAg.Comparisonofaappliedpotentials,bFEsforC andH product,cFEsforC H andEtOHand 2 2 1 2 2 4 totalC 2+productondCu 2 O/AgwithmodifiedAgatcurrentdensity800mAcm−2.dTotalcurrentdensityandeFEsforC 2+productforCO 2 RRon dCu O/Ag atselectedcellvoltageunderMEAmeasurement.fStabilitytestfordCu O/Ag atthecurrentdensity800mAcm−2inMEA.Errorbars 2 2.3% 2 2.3% correspondtothestandarddeviationofthreeindependentmeasurements. compared with dCu O and dCu O/Au , the moderate coordiincreasedwiththeappliedpotential(Fig.5b),stronglyevidencing 2 2 2.3% nationnumbersandoptimaloxidationfor Cusurface indCu O/ this process.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>This asymmetric C−C coupling has a lower energy 2 Ag result in tailored * CO configuration.</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Given the different barrier than that for *CO dimerization as evidenced by the 2.3% electron * back-donating and proton-combining ability of reported theory studies19, which contributes to increased C 2+ adsorbed CO on atop and bridge Cu sites, the energy barrier production. for following * CO protonation is altered.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2882,19 +4840,47 @@
           <t>S0521</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>The high pH at the surface of electrode is 2 thought to favor C–C coupling by lowering the energy barrier of Discussion CO 2 activation and suppressing H 2 evolution, and contributes to In summary, an assessment of a newly synthesized, silvert C h O e 2 – b T oo P s D ted for ac d t C iv u it 2 y O/ f A or g 2.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>C 3% O a 2 R ls R o . ex M hi o b r i e t o a ve h r i , gh t e h r e te C m O p – e T ra P t D ure a f n o d r E m t o O d H ifie p d at c h o w p a p y er i - s o a x c id ce e le c r a a t t a e l d yst vi h a a t s ri c g o g n e fi ri r n m g e t d he th a a s t y t m he m C et O ri 2 c R C R – t C o CO 2 andCOdesorptionthanthosefordCu 2 OanddCu 2 O/Au 2.3 , coupling.AnoptimizeddCu 2 O/Ag 2.3% exhibitsaFEof40.8%and i a n n d d ica C ti O ng fo d r Cu e 2 ffi O c / i A en g t 2.3 C % O h 2 a R s R st a ro t n l g a e r r ge bo c n u d rr in en g t st ( r S e u n p g p th lem o e f n C ta O ry 2 b E o E o H s F te o d f E 2 t 2 O .3 H % p f a o r r tia E l tO cu H rre p n r t o d d e u n c s ti i o ty n o i f n 32 fl 6 o . w 4m ce A ll, cm to − ge 2 th at er − w 0. i 8 th 9 Fig. 30).</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>V (with an 85 % iR correction).</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2916,19 +4902,43 @@
           <t>S0522</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" t="n">
+        <v>6</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-023-36411-5 Fig.4|StructuralcharacterizationofCu(OD)0.8Ag0.2catalystafterCOreducthecorrespondingatomicallyresolvedEDSmappingofCuandAgattheselected tionreaction.aTEMimageofCu(OD) Ag catalystcross-sectioncutbyFIB. interfacearea.TheatomicratiobetweenCuandAgattheinterface(i.e.,thearea 0.8 0.2 bElectrondiffractionpatternofCu(OD) Ag catalystshownina.cHAADF-STEM withinthegreenbox)wasdeterminedtobe1.12:1. 0.8 0.2 imageandcorrespondingEDSmappingofCuandAg.dHAADF-STEMimageand astheCObindingstrengthissignificantlyloweronAgthanonCu30,54. interfacial sites with relative weak CO adsorption energies on all Thus,itisreasonabletodeducethattwotypesofCusitesarepresent sampleswithdifferentelementratioandballmillingtime. on Cu(OD) 1−x Ag x catalysts, i.e., native Cu(OD) sites, and weak CO Enhanced formation of C 2+ liquid products on Cu(OD) 1−x Ag x adsorption sites consist of Cu atoms located at the interface of could be attributed to the lower C and OH affinities of the Cu–Ag immiscible Cu and Ag particles, whose electronic structure is likely interfacialsites,whichhavebeenpredictedtofavoroxygenatesover modified by the neighboring Ag atoms.</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The weak CO binding sites ethylene30,31.TheRDSforC productformationsontheCusurface 2+ identified by in situ SEIRAS on the Cu(OD) 1−x Ag x , as compared to wassuggestedtobetheCO ad hydrogenationtoCOH ad byourrecent Cu(OD), can be assigned to the Cu–Ag interfacial sites.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2950,19 +4960,47 @@
           <t>S0523</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ThisworkdescribesthedesignandrealizationoftunableinterFE of H evolution on hydrophobic-treated Cu catalyst decrea2 facialwettabilitythroughusingalkanethiolswithdifferentalkylchain sesrapidlytobelow10%(Fig.2a).Simultaneously,theFEforCOdrops lengths.Then,thelocalconcentrationofCO andH Ocanbemodufrom26.1%to2.7%andthenincreasesto8.9%.Withtheincreasingof 2 2 latedbychangingCO andH Otransportthroughdifferentinterface hydrophobicity(contactangle:from43°to131°),theFEofC (ethy2 2 2+ wettability, which may achieve an optimized equilibrium of kineticlene, ethanol, propanol) increases from 55.4% to 86.1%, with correcontrolled*COand*Hinacontrollablemanner.Thiolcanbeanchored sponding current density from 91.4 to 103.3mAcm−2 (Fig. 2b). ontheCusurfacethroughcoordinationbinding34.Wettabilitycanbe Interestingly, as the hydrophobicity further increases to a contact controlledbythelengthofanalkylchain,whichcaneffectivelyblock angleof156°,theFEandpartialcurrentdensityofC decreasesig2+ theabsorptionofwaterandfacileCO transport.Asaresult,theratio nificantly.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>With the increasing current density, the C Faraday effi2 2+ ofproducedethanoltoethylenecanbetunedinthewiderangeafter ciencyremainsatahighlevel,leadingtoanincreasedpartialcurrent hydrophobictreatment(from0.90to1.92)withremarkableFaradaic densityofC products.Thus,aC Faradaicefficiencyofupto80.3% 2+ 2+ efficiencies (FE) of ethanoland C (up to 53.7% and 86.1%, respeccan be maintained even at a high current density of 400mAcm−2, 2+ tively).</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Based on the establishment of this structure, the effect of correspondingtoaC partialcurrentdensityof321mAcm−2,whichis 2+ interfacialwettabilityonthepathwaysofethyleneandethanolisfuramongthebestperformances(Fig.2c,SupplementaryTable2).Further revealed through in-situ spectroscopy and computational fluid thermore, the ethanol-to-ethylene ratio increases from 0.90 to 1.93 dynamicsimulation. andsubsequentlydropsto1.13withtheincreasingofcontactangle from 43° to 131°.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2984,19 +5022,47 @@
           <t>S0524</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-023-36926-x Fig.1|Computationalstudiestoidentifytheoptimalpathforelectrochemical R5.Theblack-filledtriangleandred-filledcirclerefertothereactionenergyfor C–Ccouplingonbinarysites.aEnergy-global-optimisationscheme.Thered,blue, Cu211andCuZnZn(themostpromisingsite).Thesubscriptindicatestheadsorption andblackpathsshowdifferentreactionchannels,wherer ,r ,r refertothe site.R1–R9aredetailedinSupplementaryTable5.dActivationenergiesfor A B C limitingstepinrelevantpaths(SupplementaryFig.5).bScreeningofCOadsorption CO*–CO*couplingonCuandCuZn(211).eActivationenergies(blackforCu,blue energiesonCu-basedbinaryactivesites.CuMCuandCuMMrefertothebridgesites forCuZnCu,andredforCuZnZn)plottedagainstthecorrespondinglimiting fortheadsorbatebindingbetweentwoCuatoms,andCuandMatoms,whereMis potentialsoftherelevantpaths(pathsIandVforCO*–CHO*,pathsIIandVIfor thefirstneighbouratomofCu(SupplementaryFig.4).Theyellowbandshowsthe CO*–COH*,andpathsIIIandIVforCO*–CO*;SupplementaryTable6).Thesquares, expectedpromisingactivities.cReactionphasediagramforCO2RtoC2+at−0.6 triangles,andcirclesshowCO*–CO*,CO*–CHO*,andCO*–COH*couplingsteps.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>VRHE.Thedashedlines(red:C–Ccouplingsteps,blue:protonationsteps)indicate Theempty,filled,andshadedsymbolscorrespondtothe(111),(211),and(100) thereactionfreeenergiesforallconsideredelementarysteps.Thesolidlines surfaces.fReactionratescalculatedusingmicrokineticmodelsforCORtoC at 2 2+ indicatetheG -limitingstepsandenergies.Thepoints(triangleandcircles)show −0.6V (Methods).</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>RPD RHE thelimitingenergiescalculatedasthemaximumofthereactionenergyofR1and electrochemicalCO 2 Rperformance,wesprayedtheCu x Zn 1−x (x=0.95, 0.85, 0.8) and Cu surfaces at different potentials in a homemade 0.9, 0.85, 0.8, 0.7) model catalysts and commercial Cu catalysts flow-cellsystem(SupplementaryFig.12).AsshowninFig.2c,d,and (Aladdin, Product No.: C103844-10G, 80–100nm) on polytetraSupplementary Figs. 13, 14, characteristic Raman peaks were fluoroethylene (PTFE) substrates.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3018,19 +5084,47 @@
           <t>S0525</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>VRHE.Thedashedlines(red:C–Ccouplingsteps,blue:protonationsteps)indicate Theempty,filled,andshadedsymbolscorrespondtothe(111),(211),and(100) thereactionfreeenergiesforallconsideredelementarysteps.Thesolidlines surfaces.fReactionratescalculatedusingmicrokineticmodelsforCORtoC at 2 2+ indicatetheG -limitingstepsandenergies.Thepoints(triangleandcircles)show −0.6V (Methods).</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>RPD RHE thelimitingenergiescalculatedasthemaximumofthereactionenergyofR1and electrochemicalCO 2 Rperformance,wesprayedtheCu x Zn 1−x (x=0.95, 0.85, 0.8) and Cu surfaces at different potentials in a homemade 0.9, 0.85, 0.8, 0.7) model catalysts and commercial Cu catalysts flow-cellsystem(SupplementaryFig.12).AsshowninFig.2c,d,and (Aladdin, Product No.: C103844-10G, 80–100nm) on polytetraSupplementary Figs. 13, 14, characteristic Raman peaks were fluoroethylene (PTFE) substrates.</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Volcano-shaped curves were observedat~280and370cm−1,attributedtofrustratedrotationand obtainedfortheC Faradaicefficiency(FE).Notably,at150mAcm−2, stretching vibrations of Cu–CO bonds27, at ~1900–2100cm−1, 2+ theC FEoftheCu Zn modelcatalystwas considerablyhigher attributedtostretchingvibrationsofC≡Obonds(bridge-typeCO 2+ 0.9 0.1 than that of the commercial Cu catalyst(66±2% and ~50%, respecat1900–2000cm−1andatop-typeCOat2000–2100cm−1)27,28,andat tively;SupplementaryFig.10andTable10).Further,fortheCu Zn 2800–3000cm−1,attributedtoC–Hstretching29.TheaboveRaman 0.9 0.1 modelcatalyst,theC /C ratioof~11washigherthanthatof~6forthe bandsdisappearedwhenArwasusedinsteadofCO underthesame 2+ 1 2 commercialCucatalyst(SupplementaryFig.11). electrochemical conditions (Supplementary Fig. 13f), confirming Consideringtheaboveresults,weco-sputteredCu y Zn 1−y (y=0.95, that the above observed Raman peaks were representative of CO 0.9,0.85,0.8)catalystsonPTFEgas-diffusionelectrodes.Thethickadsorptiononthesurfaces.RightafterflowingCO ,quickrecovery 2 nessofthesputteredCu y Zn 1−y was~200nm,whichenabledashort of the Cu–CO, C≡O, and C–H stretching peaks were observed, distance for CO 2 diffusion from PTFE to the Cu y Zn 1−y surface. suggesting fast CO 2 R and C–C coupling on Cu 0.9 Zn 0.1 (SuppleRemarkably, the CO 2 -to-ethylene onset potential with the co-sputmentaryFig.13g).ForalltheCuandCu y Zn 1−y surfaces,theRaman tered,best-performingCu Zn (−0.3V )was~0.16Vsmallerthan peakat~370cm−1wasslightlyred-shiftedasthepotentialbecame 0.9 0.1 RHE thatwithpureCuunderthesamereactionconditions(Fig.2a).The more negative, consistent with the electrochemical Stark effect27.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3052,19 +5146,47 @@
           <t>S0526</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-023-36926-x Fig.2|ElectrochemicalandinsituRamananalysesfortheco-sputtered potentialsduringCO2R.eInsituRamanpeaksat250–470,1750–2300cm−1and Cu y Zn 1−y (y=0.95,0.9,0.85,0.8)andCucatalystsin0.75MKOHelectrolyte. 2700–3200cm−1.fC 2+ /C 1 FEs.Errorbarsrepresentthestandarddeviationbasedon aTheCH partialcurrentdensityneartheonsetpotentials.bTafelplotsforCH. threeindependentmeasurements.Allpotentialsarewithrespecttothereversible 2 4 2 4 InsituRamanpeaksforCOadsorptiononcCu0.9Zn0.1anddCuatvarious hydrogenelectrodes(RHE). consistentwiththeethyleneonsetpotentialintheelectrochemical promotetheC–Ccouplingkineticsinelectrolytes,consideringthe tests.TheC–Hstretching(2800–3000cm−1)islikelyattributedto factoflowgas-phaseCOsolubilityinaqueoussolutions. intermediatescontainingC–Hbondssuchas(1)C H O*29–theC To further improve the CO -to-C activity, we developed an 2 2 2+ 2 2+ intermediateafterC–Ccouplingandhydrogenation,or(2)CHO*or alloying–dealloying strategy to synthesize nanoporous Cu Zn 0.9 0.1 COH*30–thekeyintermediatesforC–CcouplingviatheCO*–CHO* catalysts on PTFE over a large area (Fig. 3a, b, and Supplementary and CO*–COH* pathways.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>The Raman signals of CO 2− and HCO − Figs.15,16).ThesputteredCuformscontinuousfilmlayersontopof 3 3 were observed in electrolytes at pH 7 and 13.5.</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In clear contrast, PTFE,differentfromthenanoporousstructureofCu Zn afterwet 0.9 0.1 therewasnoCO 2−andHCO −signalinelectrolytesatpH1and4 etching.Thenanoporousstructureoffersafavourablelocalenviron3 3 during in situ Raman measurement (Supplementary Fig. 14).</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3086,19 +5208,47 @@
           <t>S0527</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>For example, by comparing various to obtain sufficient enhancement of the Raman signals. 2 single-crystal surfaces with different surface roughness, we previously Similar to the oxide-derived Cu (OD-Cu) materials, which are showed that undercoordinated Cu sites are required for C formation24. selective for C–C coupling24–27, the as-prepared Cu electrode with a 2 However, it is important to further close this knowledge gap by unravelhigh electrochemical surface roughness factor (14.6; Supplementary ling how Cu coordination and local stress under reaction conditions Fig. 6, electropolished Cu foil as a reference) shows high performance affect the catalytic behaviour and thus the full mechanistic picture.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>To towards C products and provides the opportunity to detect C–C cou2+ this end, it is required to overcome the challenging low surface coverpling intermediates25.</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The specific current densities increase up to at ages of intermediates due to their short lifetimes as well as disentangle least −1.1 V (Fig. 1e), while the Faradaic efficiencies of CORR products 2 the similarities in the vibrational properties of different C–C coupling and H vary strongly with the applied potential (Fig. 1f).</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3120,19 +5270,47 @@
           <t>S0528</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>At a poten1,595 cm−1 from −0.85 V , which show a regular shift with the potential, x RHE tial of −0.36 V , the CuO is reduced to metallic Cu on the surface, and indicating the existence of new adsorbates.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>These peaks appeared RHE x a small peak is detected at 1,070 cm−1, typically assigned to carbonsimultaneously during the time-resolved in situ SERS experiment after ate13.</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Two new peaks at ∼1,390 cm−1 and ∼1,610 cm−1 appear, which are a potential switch from −0.36 V RHE to −0.96 V RHE (Supplementary Fig. 14). attributed to the symmetric and asymmetric stretching vibrations Concurrently, a broad band in the range of 2,830–2,990 cm−1 appeared, of carboxyl(ate) groups, respectively, based on control experiments which can be attributed to the stretching band of C–H (ref. 12). in Ar-saturated NaClO with 1 mM HCOOH solution (Supplementary 4 Fig. 13) and in Ar-saturated KHCO solution (Supplementary Fig. 11).</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3154,19 +5332,47 @@
           <t>S0529</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>For the peak at 1,182 cm−1, no obvious shift was rations.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Simulated vibrational frequencies can be visualized through observed in the D-labelling experiment, while the low intensity in the the ioChem-BD database37 (see the explanatory tutorial in Methods 13C/12C exchange experiment did not allow for a robust determination and Supplementary Fig. 17). of the isotope-induced shift.</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In Fig. 3, we show the main reaction intermediates responsible for Since similar C–C coupling intermediates were proposed for the vibrational frequencies detected experimentally (Fig. 2a).</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3188,19 +5394,47 @@
           <t>S0530</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>DFT vibrational frequencies for *CO2−, *COCO−, OCHCH (top, left by applying a smearing of 10 cm−1 on each DFT frequency and overlapping the 3 2 to right), *HCOOH, *OCOCO2− and *OCHCH (bottom, left to right) on adsorption resulting peaks.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Inset: different CORR reaction intermediates, with H atoms s 3 2 sites with different coordination numbers, increasing from orange to black. given in white, O atoms in red and C atoms in black.</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Experimental signals at different applied potentials are indicated on top and</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3222,19 +5456,47 @@
           <t>S0531</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Moreover, the subsurface incorporation of 2 ethanol and ethylene continuously increases with increasingly negative atomic impurities such as C or O during CORR cannot be ruled out, as 2 applied potential (Fig. 5a). this could also lead to a defective Cu surface with the modified Raman To further correlate the catalyst structure, surface intermediates shifts obtained here.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Cyclic voltammetry has been used to compare the and reaction products, we carried out quasi in situ Cu LMM XAES, defect density on the Cu surface after CORR using the charge trans2 in situ SERS, cyclic voltammetry and simulations.</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>The surface of the ferred above +0.3 V (ref. 25).</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3256,19 +5518,47 @@
           <t>S0532</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" t="n">
+        <v>5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Thus, both in situ SERS and cyclic voltammetry (Fig. 5d and Supplementary Table 14).</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Four Gaussian peak functions hint at the key role of structural defects in tuning the ethylene/ethanol centred at about 2,035 cm−1, 2,075 cm−1, 2,090 cm−1 and 2,100 cm−1 ratio.</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>These defects are probably formed under reaction conditions and were used to fit the recorded potential-dependent Raman spectra. generate distinct surface sites with strong CO binding.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3290,19 +5580,47 @@
           <t>S0533</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>At −0.95 V , the CORR25,26,45,46, while flat atomically ordered surfaces mainly yield H RHE 2 2 C–O stretching bands at 2,090 cm−1 and 2,100 cm−1, assigned to atop (ref. 24).</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Moreover, defective structures and highly disordered Cu(0)/ CO adsorbed on defect Cu sites, further increase and reach a maximum Cu(I,II) interfaces created through pulsed electrolysis conditions were at −1.04 V , coinciding with the detection of the *OCHCH key interfound to significantly enhance ethanol selectivity25,45,46.</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Thus, we iniRHE x mediate and ethanol. tially assessed the role of two structural descriptors to identify defects Nature Energy | Volume 9 | December 2024 | 1485–1496 1489 ).u.a( ytisnetnI ).u.a( ytisnetnI 1,602 Raman shift (cm–1) Fig. 4 | In situ SERS measurement and DFT vibrational analysis with vibrational fingerprints on selected active sites determined by DFT simulations the isotope exchange. a, Raman spectra of species adsorbed on the for 12C and 13C (see Methods, ref. 62). c, Raman spectra of an electrochemically electrochemically treated Cu electrode at −0.95 V in 13CO-saturated 0.1 M treated Cu foil acquired in 0.05 M glyoxal for potentials ranging from −0.3 V to RHE 2 RHE NaClO electrolyte and CO-saturated 0.1 M NaClO DO electrolytes. b, OCHCH about −1.0 V in an Ar-saturated 0.1 M NaClO electrolyte. 4 2 4 2 2 RHE 4</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3324,19 +5642,47 @@
           <t>S0534</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>On crystalline domains, *CO binding depends weakly on selectivity towards C of OD-Cu25, which is due to the abundant under2 the strain, in line with results on crystalline surfaces47, while differences coordinated sites on these materials36 (about 74% for N &lt; 8 on our Cu–Cu of more than 0.4 eV are observed on highly strained low-coordinated OD-Cu model; Supplementary Fig. 16).</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Furthermore, from −0.85 V RHE OD-Cu sites (Supplementary Fig. 24 and Supplementary Table 16). onwards, undercoordinated distorted sites with high surface strain Besides, both crystalline and distorted morphologies with coordinaand deep s-band states originate (Fig. 5c,e) and enable the formation tion number below 8 show strong CO binding (&lt;−0.2 eV). of OCHCH at the surface (Fig. 6b), detected experimentally through 2 Localized compressive strain plays a crucial role in stabilizing Raman spectroscopy (Figs. 2c and 3) together with the production of *OCHCH species on distorted sites (red empty data points in Fig. 6a). ethanol (Fig. 1f). 2 In fact, *OCHCH formation energies increase following the increA careful comparison of ethylene, ethanol and methane Fara2 ment of compressive strain, and stronger binding is observed on daic efficiency versus CO selectivity (taken from Fig. 1f) confirms the undercoordinated distorted sites rather than crystalline sites.</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Such existence of key differences between the ethylene and ethanol routes difference between crystalline and distorted sites can be ascribed (Fig. 6c).</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3358,19 +5704,47 @@
           <t>S0535</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" t="n">
+        <v>8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>The cell was equipped with a reference On the basis of in situ SERS and DFT simulations, we identified the cruelectrode (leak-free Ag/AgCl, Alvatek), a counter electrode (Pt ring) cial active sites and reaction intermediates responsible for ethylene and and a Cu foil working electrode.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Typically, a 15 ml CO-saturated 0.1 M 2 ethanol formation in CORR over a Cu surface.</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>We unveiled that defects NaClO solution was used as the electrolyte, and CO was continuously 2 4 2 in Cu with a low coordination number (&lt;8) enable strong *CO binding, injected into the solution during the experiment.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3392,19 +5766,47 @@
           <t>S0536</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" t="n">
+        <v>9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DFT details Visualization of vibrational fingerprints The DFT calculations were performed using the Vienna Ab initio To visualize vibrational frequencies of a given reaction intermediate Simulation Package34,35, with the Perdew-Burke-Ernzerhof (PBE) denin ioChem-BD37, it is necessary to follow the next steps, summarized sity functional33.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>We included dispersion according to the DFT-D2 in Supplementary Fig. 17. method53,54, with the re-parametrization of C coefficients for metals 6 performed by our group55.</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>To account for solvent stabilization of (1) Access ref. 62 and click on the ‘frequencies’ collection (top left) intermediate formation energy, we employed the VASPsol code56,57.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3426,19 +5828,47 @@
           <t>S0537</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>We included dispersion according to the DFT-D2 in Supplementary Fig. 17. method53,54, with the re-parametrization of C coefficients for metals 6 performed by our group55.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>To account for solvent stabilization of (1) Access ref. 62 and click on the ‘frequencies’ collection (top left) intermediate formation energy, we employed the VASPsol code56,57.</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>(2) Select the desired item to visualize by clicking on the title ‘frq-X’ Inner electrons were represented by projector augmented wave (PAW) (3) Once a new tab opens, click on ‘Actions → View data’ (top right) pseudopotentials58,59, whereas the monoelectronic states for the (4) Once a new tab opens, scroll down to ‘vibrational frequencies’ valence electrons were expanded as plane waves with a kinetic energy and click on it cut-off of 450 eV.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3460,19 +5890,47 @@
           <t>S0538</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Kim,Y.etal.Time-resolvedobservationofC–Ccouplinginter13 zonewassampledby3×3×1k-pointsbymeansofMonkhorst-Pack mediatesonCuelectrodesforselectiveelectrochemicalCO 2 scheme with the cutoff of 400eV during the structural relaxation, reduction.Energ.Environ.Sci.13,4301–4311(2020). while 5×5×1 k-points for electronic structure calculation such as 13.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Zhang,J.etal.AcceleratingelectrochemicalCO reductionto 2 projecteddensityofstates(PDOS)andchargedensitydifference.The multi-carbonproductsviaasymmetricintermediatebindingat convergence criteria for energy and force were set as 10−5eV and confinednanointerfaces.Nat.Commun.14,1298(2023). 0.01eVÅ−1,respectively.Alongtheperpendiculardirection,avacuum 14.</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Hu,J.etal.Edge-richmolybdenumdisulfidetailorscarbon-chain space at least 18Å was added to eliminate the effects of periodic growthforselectivehydrogenationofcarbonmonoxidetohigher structure, and the dispersion corrected density functional theory alcohols.Nat.Commun.14,6860(2023).</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3494,19 +5952,47 @@
           <t>S0539</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Hu,J.etal.Edge-richmolybdenumdisulfidetailorscarbon-chain space at least 18Å was added to eliminate the effects of periodic growthforselectivehydrogenationofcarbonmonoxidetohigher structure, and the dispersion corrected density functional theory alcohols.Nat.Commun.14,6860(2023).</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>(DFT-D3) was utilized to include van der Waals (vdWs) interaction 15.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Wu,Z.-Z.etal.IdentificationofCu(100)/Cu(111)Interfacesas betweenadsorbateandinterface70.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3528,19 +6014,47 @@
           <t>S0540</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Therefore, scopy(TEM)(Fig.1bandSupplementaryFigs.1,2).AsshowninFig.1c, 2 2 regulating the key intermediates involved in the CO RR over theAgCuNWexhibitstypicalcharacteristicsofsupportedcatalyst,with 2 catalytic sites and optimizing their binding energies become criAg nanoparticles distributed as islands on the surface of the Cu NW tical to adjust the C-C coupling pathways towards targeted C (SupplementaryFigs.3,4),andobviousgrainboundariesbetweenAg 2+ products.Nevertheless,manipulationofC-Ccouplingpathwaysis nanoparticles and Cu NW can be clearly observed (Supplementary still highly challenging due to the complexity of the catalytic Fig.4b).Incontrast,AgCuNWdisplayssimilarmicrostructuralfeatures 1 system, the unclear reaction intermediates and the limited to Cu NW (Fig. 1d and Supplementary Figs. 5, 6).</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>High-angle annular mechanisticunderstanding. dark-field scanning transmission electron microscopy(HAADF-STEM), Cu-based materials have been well established as promising energy-dispersive X-ray spectroscopy (EDX) elemental mapping and electrocatalystscapabletoreduceCO tomultipleC products11,26–28. electronmicroscopy-basedatomrecognitionstatistics(EMARS)analysis 2 2+ Till now, a large number of Cu-based tandem catalysts have been on HAADF images of AgCu NW indicate that isolated Ag atoms are 1 developed to realize high selectivity in CO RR to produce C prouniformly distributed on the surface of Cu NW matrix in AgCu NW 2 2+ 1 ducts,primarilyresultingfromtheimprovedmasstransportof*CO (Fig. 1e and Supplementary Figs. 6c, d and 7)44.</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The X-raydiffraction intermediatefromCO-formationcatalystandthepromotedC-Ccou- (XRD) patterns ofCu NW and AgCu NW exhibitidenticaldiffraction 1 pling over Cu surface29–32.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3562,19 +6076,47 @@
           <t>S0541</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" t="n">
+        <v>8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Subsequently, the condition(OCV,immersedinKHCO electrolyte),−0.7and−1.2Vvs. 3 homogeneoussolutionwaskeptinawaterbathat75oCandstirredfor RHE,respectively. 24huntilthesolutionturnedbrown.Afterwards,theabovesolution wastransferredintoa150mLpressurebottleandheatedat120°Cfor OperandoXASmeasurements 24h.Aftercoolingtoroomtemperature,theproductswerecollected X-ray Absorption Spectroscopy (XAS) and operando XAS measureby centrifugation at 16099.2 (×g) for 5min.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>The obtained reddishmentswereperformedinthetotal-fluorescenceyield(TFY)modeat brownCuNWwaswashedwithhotdeionizedwater(60°C),ethanol, room temperature.</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>These measurements utilized the TPS 32A and andhexaneseveraltimestoremoveexcesshexadecylamineandgluTLS01C1 beamlines at the National Synchrotron Radiation Research cose,anddriedat60°Cundervacuumfor12h.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3596,19 +6138,43 @@
           <t>S0542</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" t="n">
+        <v>18</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
         <is>
           <t>ARTICLE IN PRESS Fig. 3 | In-situ characterization and mechanism exploration of the CO ER to EtOH.</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In-situ 2 FTIR spectra of Co -Sub-CuS in (a) 12CO -saturated 1 M KOH with H O, (b) 13CO -saturated 0.050 2 2 2 1 M KOH with H O.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3630,19 +6196,47 @@
           <t>S0543</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" t="n">
+        <v>18</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>ARTICLE IN PRESS Fig. 3 | In-situ characterization and mechanism exploration of the CO ER to EtOH.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>In-situ 2 FTIR spectra of Co -Sub-CuS in (a) 12CO -saturated 1 M KOH with H O, (b) 13CO -saturated 0.050 2 2 2 1 M KOH with H O.</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>(c) Comparison of the in-situ FTIR spectra on Co -Sub-CuS in 12CO - 2 0.050 2 saturated 1 M KOH with H O, 13CO -saturated 1 M KOH with H O and 12CO -saturated 1 M KOH 2 2 2 2 with D O.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3664,19 +6258,47 @@
           <t>S0544</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" t="n">
+        <v>18</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>(f) The calculated infrared-active vibrational 0.050 frequency of *CHCHO* on Co -Sub-CuS, the right is the different adsorption modes of two key 0.050 intermediates *CHCHO* and *CHC*OH at dual-Cu sites.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>(g) In-situ Raman peaks on Co -Sub0.050 CuS in 1 M KOH from 0.1 V vs.</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>RHE to -1.1 V vs.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3698,19 +6320,47 @@
           <t>S0545</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" t="n">
+        <v>40</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Error bars represent the standard A deviation from at least three independent measurements.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Fig. 3 | In-situ characterization and mechanism exploration of the CO ER to EtOH.</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In-situ 2 FTIR spectra of Co -Sub-CuS in (a) 12CO -saturated 1 M KOH with H O, (b) 13CO -saturated 0.050 2 2 2 1 M KOH with H O.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3732,19 +6382,47 @@
           <t>S0546</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ARTICLE IN PRESS atoms with the Cu surface—either as *CH*COH in the form of surface-C bonds17-19, or as *CHCHO* in the form of surface-O bonds17,19.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Theoretically, the latter configuration could efficiently prevent the loss of O atom in subsequent steps, thereby favoring the formation of C 2 oxygenates6,8,17,19.</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In contrast, the former configuration often occurs spontaneously due to its low free energy barrier, leading to dehydration during subsequent protonation steps and ultimately producing only C hydrocarbons5,14,17-19.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3766,19 +6444,47 @@
           <t>S0547</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" t="n">
+        <v>5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>In contrast, the former configuration often occurs spontaneously due to its low free energy barrier, leading to dehydration during subsequent protonation steps and ultimately producing only C hydrocarbons5,14,17-19.</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>In this regard, the binding strength of O atoms in the 2 *CHCHO* on the surface of Cu-based electrocatalysts could seSrve as a crucial descriptor for S evaluating the bifurcation potential between C H and EEtOH formation.</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In current Cu-based 2 4 R catalysts system, however, the experimental identPification and induction of *CHCHO* from N *CHCO have not been reported, primarily due to the uncontrollable binding of O atoms and the I uncertainty surrounding the adsorption fo E rm of the SDI8-11,16,17.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3800,19 +6506,47 @@
           <t>S0548</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" t="n">
+        <v>11</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Zhong,D.etal.CouplingofCu(100)and(110)facetspromotes The Gibbs free energies were calculated by the VASPKIT tool at a carbondioxideconversiontohydrocarbonsandalcohols.Angew. temperatureof298.15Kusingtheformula: Chem.Int.Ed.60,4879–4885(2021). 20.</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Lv,Z.etal.ImprovingCO‐to‐C conversionofatomicCuFONC 2 2 G=E +E (cid:2)TS ð7Þ electrocatalyststhroughF,O‐codrivedoptimizationoflocalcoorDFT ZPE dinationenvironment.Adv.EnergyMater.14,2400057(2024). whereE representedtheelectronicenergycalculatedbyDFT,andS 21.</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Kim,C.etal.Cu/Cu Ointerconnectedporousaerogelcatalystfor DFT 2 and E represented the entropy contribution and zero-point highlyproductiveelectrosynthesisofethanolfromCO.Adv.Funct.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3834,19 +6568,43 @@
           <t>S0549</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" t="n">
+        <v>8</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-025-63009-w theelectrolytewithCAtosomedegree,implyingarestrictedHERrate, −0.75eV,thusswitchingtheselectivityfromC H toC HOH.Conse2 4 2 5 whichmaybeduetotheenhancedinteractionofCAandH Omolequently,thepresenceofCAmoleculeaffectedtheadsorptionstrength 2 culesatthereactioninterface.Inaddition,duetotheStarkeffect,the of*OC H overCusurfaceanditsinternalC–Obond,switchingthe 2 3 vibrationalwavenumberoftheO–Hbondingdecreasedastheincrease bond cleavage order and the CO RR pathway, thus resulting in the 2 oftheelectricfield(SupplementaryFig.19).Incomparison,thesmaller impressiveC HOHselectivity. 2 5 StarkeffectoverCucatalystintheelectrolytewithCAindicatedthat thereorientationofH Owasslower,aswellasthelongerdistanceof ContinuousenrichmentofCAbypulsedelectrolysisstrategy 2 Cu–Hbond48,illustratingH Owasfarawayfromthecatalystsurfacein Aproposedinsidetoon-surfacediffusionapproachcanwellenrichthe 2 the presence of CA (Supplementary Fig. 20).</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Consequently, an anions in the Helmholtz plane indeed and manipulate the interface ordered/stable H-bond network derived from the strong intermicroenvironment.Todeeplyintensifythisprocessandalleviatethe molecularinteractionofCAwithH Omoleculesgovernedarestricted gradualdiffusionofCAintothebulkelectrolyteduetoelectrostatic 2 H O adsorptionand activation processes, further inhibited the HER repulsionduringlong-termoperation,weinnovativelyemployedan 2 kinetics. asymmetricpulsedelectrolysismethodtorebuildandrejuvenatethe DFT calculations were carried out to further understand the local chemical microenvironment, sufficiently enriching and concontributionofCAintheCO RRprocess,especiallytheeffectsofC–C tinuouslymaintainingtheCAintheHelmholtzplane.Atthesametime, 2 coupling and hydrocarbon or oxygenated multi-carbon chemicals in order to avoidthe overhigh positive potential during pulse elecselectivity.Thermodynamically,Cu(100)facetwasconducivetoC–C trolysisaffectingthestructureandmorphologyoftheCucatalyst,a coupling,whichwasverifiedbypreviouswork49,50.Consequently,we specific asymmetric pulse electrolysis procedure was designed, i.e., constructedaCu(100)catalystmodelwithandwithoutaCAmolecule −1.6V for 15min, then rapidly switching to 0.1V for 5min (Fig. 6a, adsorbedonthesurface(denotedasCu(100)-CAandCu(100),SupSupplementaryFig.24).Thiscontinuousdynamicpotentialswitching plementary Data1).</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3868,19 +6626,47 @@
           <t>S0550</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>It is reasonable to assume that there is subInsitusurface-enhancedRamanmeasurements.Tounderstand stantial hydrogen bonding between Cu-OH and the H in the the mechanism through which co-electrolysis of CO and O surroundingwatermolecules,whichwillimpactonthefrequency 2 2 boosts the CO 2 RR activity, in situ SERS is employed to identify oftheCu-OHmode.WhenreplacingH 2 OwithD 2 O,wenotonly surface species presenting during the co-electrolysis36.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>The Cu replace Cu-OH with Cu-OD, but also replacing the surrounding microparticle catalysts employed in this work readily exhibit the H 2 OwithD 2 O,thus thechangeinthereduced mass isexpected surface enhancement of Raman signals, which alleviate the need to be more significant than that without the hydrogen-bonded to introduce SERS-inducing particles37,38, and is consistent with water.Thepossibilityofthisbandat706cm −1correspondingto several recent studies36,37,39.</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In the Ar atmosphere (Fig. 3a), anadsorbedC-containingspeciesisruledoutbytheobservation multiple peaks at146,219,412, 528,and 619cm −1 are observed thatthisbandonlyappearinO 2 containedelectrolytebutnotin at the open circuit potential (OCP) and can be attributed to the pure CO 2 or Ar saturated electrolyte (Fig. 3).</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3902,19 +6688,47 @@
           <t>S0551</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>H 2 O 2 is a Density functional theory calculations.</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>To further evaluate the possible product of the ORR via the 2-electron pathway43.</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>If hypothesized beneficial effect of the hydroxyl group on the producedduringtheco-electrolysisofCO 2 andO 2 onCu,H 2 O 2 CO 2 RR, potential energy landscapes of key reaction steps are )2–mc Am( j )2–mc Am( j laitrap laitrap ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-020-17690-8 a b c 6 10 –0.75 V –0.80 V –0.85 V RHE ×3.5 ∞ RHE ×5.1 RHE ×4.8 5 8 C products HER C products HER C products HER 1 1 1 4 6 ∞ ∞ ×6.6×6.0 ×3.8 ×1.7 3 ×2.6 ×2.2 4 ×2.3 2 ×3.1 ×2.5 ×2.3 ×2.1 ×1.8 ×1.2 ×1.8 ×1.4 1 ∞ 2 ∞ 0 0 Methane CO Formate Hydrogen Methane CO Formate Hydrogen Methane CO Formate Hydrogen d e f 16 20 –0.90 V –0.95 V –1.00 V RHE RHE RHE ×3.1 ×2.7 ×3.6 C products HER 12 C products HER 15 C products HER 1 1 1 ×2.2 8 ×1.7 10 ×1.8 ∞ ×12 ×11 ×35×34 ∞ 4 ×0.5 ×0.7 5 ×0.7×0.7 ×0.7 ×0.4 ×0.6 ×0.3 ×0.6 ×0.4 ×0.3 ×0.5 0 0 Methane CO Formate Hydrogen Methane CO Formate Hydrogen Methane CO Formate Hydrogen Pure CO 10% O + 90% CO 20% O + 80% CO 2 2 2 2 2 Fig.2ComparisonofC productandH formations.ThepartialcurrentdensitiesofC productsandH measuredat100%CO ,10%O +90%CO ,and 1 2 1 2 2 2 2 20%O +80%CO arecomparedatdifferentpotentialsofa−0.75V ,b−0.80V ,c−0.85V ,d−0.90V ,e−0.95V ,andf−1.0V . 2 2 RHE RHE RHE RHE RHE RHE ThenumbersstandfortheenhancementrelativetotheratesatpureCO .Theerrorbarsrepresentthestandarddeviationfromatleastthreeindependent 2 measurements. 4 NATURECOMMUNICATIONS| (2020) 11:3844 |https://doi.org/10.1038/s41467-020-17690-8|www.nature.com/naturecommunications</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3936,19 +6750,47 @@
           <t>S0552</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>100 estimated via density functional theory calculations.</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>The free experiments showing that polycrystalline Cu leads to a product energy profiles of the rate-determining steps (RDS) in the fordistribution similar to that on Cu(100)48.</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Therefore, Cu(100) mation of C 2+ products, i.e., *CO dimerization29,31,44,45 and facet is commonly used as a representative model surface for methane, i.e., *CO hydrogenation29,44,46, are calculated at difobtaining theoretical insights into experimental studies based on ferent*OHcoverageontheCu(100)facet,withtherepresentative polycrystalline Cu46,49.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3970,19 +6812,47 @@
           <t>S0553</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>The energies of *OH coverageincreases.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Thiscould be attributed to theincrease initial structures fluctuate slightly within an energy range of of oxidation state of surface Cu as revealed by Bader charge 0.2eV when *OH coverage increases, however, the transition analysis (Supplementary Fig. 12), which weakens the π-backstate of *CO hydrogenation is stabilized under same conditions. donation from the Cu to the anti-bonding orbital of the C≡O We speculate that this is likely due to the transition state forms bond51,52.</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The magnitude of destabilization of the initial state is additionalhydrogenbondswith*OHgroupsathighercoverage. greaterthanthatofthetransitionstatewhenthe*OHcoverageis The stabilization of reactant by forming hydrogen bonds with at or below 3/9, leading to the decrease of the reaction barrier.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4004,19 +6874,47 @@
           <t>S0554</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Thiscould be attributed to theincrease initial structures fluctuate slightly within an energy range of of oxidation state of surface Cu as revealed by Bader charge 0.2eV when *OH coverage increases, however, the transition analysis (Supplementary Fig. 12), which weakens the π-backstate of *CO hydrogenation is stabilized under same conditions. donation from the Cu to the anti-bonding orbital of the C≡O We speculate that this is likely due to the transition state forms bond51,52.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>The magnitude of destabilization of the initial state is additionalhydrogenbondswith*OHgroupsathighercoverage. greaterthanthatofthetransitionstatewhenthe*OHcoverageis The stabilization of reactant by forming hydrogen bonds with at or below 3/9, leading to the decrease of the reaction barrier.</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>*OH has been reported in a previous work53. 6 NATURECOMMUNICATIONS| (2020) 11:3844 |https://doi.org/10.1038/s41467-020-17690-8|www.nature.com/naturecommunications</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4038,19 +6936,43 @@
           <t>S0555</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>The selective generation of toward ethylene production as compared to pure CuO 2+ 2 liquidproductssuchasethanol,1-propanol,andacetaldehyde nanowires.[11] Furthermore, CuAg surface alloys have been is highly desirable due to their high energy densities and foundtobemoreselectivefortheformationofmulti-carbon advantages for storage/transport as compared to gaseous products than pure copper.[12] The facilitated yield of C 2+ products.[2] products in the bimetallic system is usually linked to the suppression of HER due to the enhanced coverage of *CO adsorbates as compared to *H,[12b] and the diffusion of CO [*] A.Herzog,Dr.A.Bergmann,Dr.H.S.Jeon,Dr.J.Timoshenko, from Ag sites to Cu sites that enables C@C coupling (CO Dr.S.Kfhl,C.Rettenmaier,M.LopezLuna,F.T.Haase, spillover).[10,11] Note here that a short diffusion path of CO Prof.Dr.B.RoldanCuenya DepartmentofInterfaceScience and therefore a homogeneous distribution of Cu and Ag at Fritz-HaberInstituteoftheMax-PlanckSociety the surface of the catalyst are essential for an effective CO Faradayweg4–6,14195Berlin(Germany) spillover.[10,12b]Nonetheless,althoughthespatialarrangement E-mail:roldan@fhi-berlin.mpg.de ofCuandAginthesestudiesseemstoplayakeyroleforthe SupportinginformationandtheORCIDidentificationnumber(s)for differentCORRselectivitytrendsobtained,thekeyparamtheauthor(s)ofthisarticlecanbefoundunder: 2 eters for achieving an optimal synergy in Cu–Ag bimetallic https://doi.org/10.1002/anie.202017070. systems are still unknown.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>In particular, open questions still T2021TheAuthors.AngewandteChemieInternationalEdition remain on the composition and structure of the most active publishedbyWiley-VCHGmbH.Thisisanopenaccessarticleunder and C -selective systems under operando CORR condithetermsoftheCreativeCommonsAttributionLicense,which 2+ 2 permitsuse,distributionandreproductioninanymedium,provided tions,includingthestabilityofCu 2 O,whichmightbemodified theoriginalworkisproperlycited. byintroducingAg.[13] 7426 T2021TheAuthors.AngewandteChemieInternationalEditionpublishedbyWiley-VCHGmbH Angew.Chem.Int.Ed.2021,60,7426–7435</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4072,19 +6994,47 @@
           <t>S0556</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>We conCu 2 ONCs,3-Ag/Cu 2 O,and5-Ag/Cu 2 O,andof5-Ag/Cu 2 Odepositedoncarbon clude that the hollow structures paperafter2hofCORRat@1.0V . 2 RHE afterCORR(Figure1)mightcon2 sist of a mixture of CuO and Cu 2 Table1showstheas-preparedcompositionandcoherence crystallites as seen in XRD.</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>The coherence length of the length derived from Rietveld refinement of the XRD metallic Ag phase is on average slightly decreased after patterns.ThecoherencelengthofCuOagreeswellwiththe CORR,whichagreeswiththepartialre-dispersionofAgon 2 2 size distribution obtained by STEM analysis, although it is theCusurfaceandtheAg-richdomainslikelybeingformed slightly smaller than the mean NC edge length.</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The atomic frommultipleAgNPs. fractions of metallic Ag in the as-prepared Ag/CuO agree Quasi-in situ X-ray photoelectron spectroscopy (XPS) 2 well with the Cu/Ag composition obtained by ICP-MS measurementswereperformedtogaindeeperinsightintothe (TableS5).</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4106,19 +7056,47 @@
           <t>S0557</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" t="n">
+        <v>7</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>At more negative potentials, the operando SERS data of the AgNPdecoratedCuONCsexhib2 it significant differences compared to the bare CuONCs during CORR: 2 2 1)At higher Raman shifts, a broad band of the C@O vibrations appeared at 2088cm@1 for CuONCs 2 during CORR, while for 2 Ag/CuO a shoulder at 2 2031cm@1 is more pronounced.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>This might be assignedtothemultisitebinding mechanism on the AgCu surface, where each Figure6.</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>ModuliofFourier-transformedCuandAgK-edgeEXAFSspectraofCuONCs(black),3-Ag/CuO binding configuration has 2 2 (blue),and5-Ag/CuO(green)intheas-preparedstate(a,c)andinthefinalstateunderoperandoCO a different electron back2 2 reductionconditionsat@1.0V (b,d)withcorrespondingfits(red).PartialcontributionofAg@Cubonds,as donating ability.[17] 2)For RHE obtainedfromEXAFSdatafitting,isalsoshownin(d)withdottedlines.ReferencespectraofCu 2 O,Cuand the AgNP-decorated Agfoilsareshownforcomparison.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4140,19 +7118,47 @@
           <t>S0558</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Preparation of Cu NCs and Electrodes.</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Cu NCs were OperandoXASmeasurementswereperformedattheP64beamline prepared by modifying a previously reported procedure.32,33 In a of thePETRA-IIIsynchrotron(Hamburg,Germany).Time-resolved typical synthesis, a dilute alkaline solution containing Cu ions was quickX-rayabsorptionfinestructure(QXAFS)spectrawerecollected prepared by adding 8 mL of a CuSO·6HO solution (0.1 M) and influorescencemode.Ahomemadeflowcellwasusedtoacquirethe 4 2 28 mL of a NaOH solution (1 M) to 732 mL of ultrapure water at XASspectraunderthereactionconditions.Intheoperandoflowcell,a roomtemperature.Afterthemixturewasstirredfor10s,32mLofan KaptonwindowwasinstalledtoallowX-raystoilluminatethecatalyst L-ascorbicacidsolution (0.25M)was added.The solutionwas then on the GDE from the back and collect the emitted fluorescence stirredforafurther13min.Thesolutionwascentrifugedandwashed (Figure S2).</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>All samples were measured in air and under operando severaltimeswith waterand ethanol. conditions corresponding to potentiostatic and pulsed electrolysis.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4174,19 +7180,47 @@
           <t>S0559</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>All samples were measured in air and under operando severaltimeswith waterand ethanol. conditions corresponding to potentiostatic and pulsed electrolysis.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>To prepare the electrodes on a GDE, a catalyst ink was made by The details of the XAS data acquisition and processing, as well as dispersing 0.5 mg of the catalyst powder with ∼22 wt % of Nafion schematics of the flow cell employed, are given in Supplementary (relative to the total loading, Sigma-Aldrich) in 1 mL of methanol.</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Note 2 inthe SupportingInformation. 7579 https://doi.org/10.1021/jacs.1c03443 J.Am.Chem.Soc.2021,143,7578−7587</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4208,19 +7242,47 @@
           <t>S0560</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" t="n">
+        <v>7</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>These Cu O bands were Cu O species during the anodic pulse.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>This condition would 2 2 2 morepronouncedatE valuesover1.0V.Therefore,ingood leadtolocalOHconsumption,resultinginarapiddecreasein an agreement with the operando XAS data, SERS data also the local pH near the surface of the catalyst.</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The locally indicatedthatthepulsedelectrolysisathighE valuesresulted reduced pH may make the reaction pathway favorable toward an in the accumulation of Cu O species.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4242,19 +7304,47 @@
           <t>S0561</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" t="n">
+        <v>7</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>This condition would 2 2 2 morepronouncedatE valuesover1.0V.Therefore,ingood leadtolocalOHconsumption,resultinginarapiddecreasein an agreement with the operando XAS data, SERS data also the local pH near the surface of the catalyst.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>The locally indicatedthatthepulsedelectrolysisathighE valuesresulted reduced pH may make the reaction pathway favorable toward an in the accumulation of Cu O species.</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>An important finding CH production.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4276,19 +7366,47 @@
           <t>S0562</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" t="n">
+        <v>8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>CONCLUSION Institute of the Max-Planck Society, 14195 Berlin,Germany FelixT.Haase−DepartmentofInterfaceScience,Fritz-Haber In summary, we have explored the effect of a pulsed CO 2 Institute of the Max-Planck Society, 14195 Berlin,Germany electroreduction procedure on the selectivity of a Cu NC catalyst in a gas-fed flow cell configuration.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Our results Complete contact information is available at: demonstratethatthehydrocarbonselectivitycanbeeffectively https://pubs.acs.org/10.1021/jacs.1c03443 controlledandthatonecanswitchbetweenC andC product 1 2 formation by properly choosing the pulsing conditions.</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Notes Operando spectroscopy and ex situ microscopy measurements T■he authors declare no competing financial interest. revealedthatsuchselectivitytrendscanbeassignedtodifferent factors.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4310,19 +7428,43 @@
           <t>S0563</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
         <is>
           <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-021-27456-5 Fig.1StructuralandelementalcompositionofthefunctionalizedAg–Cucatalysts.aSchematicrepresentationofthefunctionalizedAg–Cuelectrodesin amembraneelectrodeassembly.b,cCross-section(b)andtop-view(c)scanningelectronmicroscope(SEM)imagesofthefunctionalizedhierarchical Ag–Cucatalystonagasdiffusionelectrode(GDE).dHigh-angleannulardark-fieldscanningtransmissionelectronmicroscopy(HAADF-STEM)image (left)andcorrespondingCu(red)andAg(blue)EDSelementalmapsofN SN-functionalizedAg–Cu(right).eHigh-resolutiontransmissionelectron 2 microscope(HR-TEM)micrographoftheN SN-functionalizedelectrode(e).fHAADF-STEMimageandthecorrespondingCuandSEDSelementalmaps 2 takenfromasectionofCusurfaceontheN SN-functionalizedAg–Cuelectrode.gHAADF-STEMimageoftheCusurfaceofN SN-functionalizedAg–Cu. 2 2 h(top),Electronenergy-lossspectroscopy(EELS)elementalmappingofCtakenfromtheareamarkedbytheboxing.h(bottom),EELSspectrumofthe C-KedgewithfinestructurescharacteristicsofcarbonlinkedtoheteroatomsfromN SNlayerontheCusurface.iRamanspectraofpristine(non2 functionalized)Ag–Cu(gray),C -functionalizedAg–Cu(orange),C N-functionalizedAg–Cu(green),N N-functionalizedAg–Cu(purple)andN SN3 2 3 2 functionalizedAg–Cu(blue). clarifytheorientationofthearomaticheterocyclesonthecatalyst evaluated the Faradaic efficiency (FE) by using nuclear magnetic surface, we carried out density functional theory (DFT) calcularesonance (NMR) and gas chromatography (GC) (See details in tions to estimate the total energy and the binding energy of the Methods section).</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>H 2 , CO, formate, CH 4 , and C 2+ products thiadiazole on Cu using a model with 5 Cu (111) slabs (Supplewereformedonthebimetallicelectrode(SupplementaryFig.14). mentary Figs. 12 and 13).</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4344,19 +7486,47 @@
           <t>S0564</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-021-27456-5 Fig.1StructuralandelementalcompositionofthefunctionalizedAg–Cucatalysts.aSchematicrepresentationofthefunctionalizedAg–Cuelectrodesin amembraneelectrodeassembly.b,cCross-section(b)andtop-view(c)scanningelectronmicroscope(SEM)imagesofthefunctionalizedhierarchical Ag–Cucatalystonagasdiffusionelectrode(GDE).dHigh-angleannulardark-fieldscanningtransmissionelectronmicroscopy(HAADF-STEM)image (left)andcorrespondingCu(red)andAg(blue)EDSelementalmapsofN SN-functionalizedAg–Cu(right).eHigh-resolutiontransmissionelectron 2 microscope(HR-TEM)micrographoftheN SN-functionalizedelectrode(e).fHAADF-STEMimageandthecorrespondingCuandSEDSelementalmaps 2 takenfromasectionofCusurfaceontheN SN-functionalizedAg–Cuelectrode.gHAADF-STEMimageoftheCusurfaceofN SN-functionalizedAg–Cu. 2 2 h(top),Electronenergy-lossspectroscopy(EELS)elementalmappingofCtakenfromtheareamarkedbytheboxing.h(bottom),EELSspectrumofthe C-KedgewithfinestructurescharacteristicsofcarbonlinkedtoheteroatomsfromN SNlayerontheCusurface.iRamanspectraofpristine(non2 functionalized)Ag–Cu(gray),C -functionalizedAg–Cu(orange),C N-functionalizedAg–Cu(green),N N-functionalizedAg–Cu(purple)andN SN3 2 3 2 functionalizedAg–Cu(blue). clarifytheorientationofthearomaticheterocyclesonthecatalyst evaluated the Faradaic efficiency (FE) by using nuclear magnetic surface, we carried out density functional theory (DFT) calcularesonance (NMR) and gas chromatography (GC) (See details in tions to estimate the total energy and the binding energy of the Methods section).</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>H 2 , CO, formate, CH 4 , and C 2+ products thiadiazole on Cu using a model with 5 Cu (111) slabs (Supplewereformedonthebimetallicelectrode(SupplementaryFig.14). mentary Figs. 12 and 13).</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Among the different configurations Remarkably,theFaradaicefficiencyforC andH —obtainedvia 1 2 tested, the adsorption of thiadiazole is more stable when the the CO RR and HER—decreased after functionalization with 2 N 2 –N 3 nitrogen atoms of the diazole sit on Cu (111) and the thiazole and thiadiazole, while the FE for C 2+ products sharply binding energy is estimated to be −1.08eV—at least 0.37eV increases (Fig. 2b).</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4378,19 +7548,47 @@
           <t>S0565</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>To better evaluate the selectivity of electrodesatapotentialof−1.2Vvs.RHEformorethan20hin 2 C 2+ products on thiadiazoleand triazole-functionalized Ag–Cu the H-cell reactor, while recording the current density and electrodes, we calculated the ratio in FE for C 2+ products and continuously analyzing the products of the reaction (Supplemenhydrogen (FE C 2þ =FE H 2 ) (Fig. 2e).</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Compared with pristine and t d a e r m y o F n i s g t . rat 2 e 0 d ). st T ab h l e e p N er 2 f S o N rm - a a n n c d e w N it 3 h Na fu r n et c e t n io t n io a n liz o e f d th e e le c c u tr r o r d en es t alkyl-functionalized electrodes, both N SN and N N functional groupspresentthelargestFE =FE ra 2 tios—illustr 3 atingthatthe densityof94%and91%respectively—sharplyimprovedcompared functionalizationwitharoma C ti 2 c þ hete H ro 2 cyclesefficientlydirectsthe N to N tha fu t n o c f ti p o r n is a t l i i n ze e d A A g g – – C C u u a e t le 7 c 8 tr % o . d T es h r e em FE ain fo s r a C s 2 h + igh of a N s5 2 S 4 N %a an n d d reaction pathway towards the formation of C 2+ products while 46 3 .5% after 20h, which demonstrates that the selectivity for the suppressing the HER.</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>To get a more accurate estimation of the reaction pathway on the surface of the electrode is not modified intrinsic CO 2 RR performance of the functionalized Ag–Cu elecduringelectrolysis.Tofurtherconfirmtheapparentstabilityofthe trodes, we estimated the electrochemically active surface area of functionalized electrode, we performed XPS spectroscopy to Cu(CuECSA)andAg(AgECSA)forthe15at.%Ag–Cuandthe evaluate the N:Cu ratio after 30min, 1h, 24h, and 100h.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4412,19 +7610,47 @@
           <t>S0566</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" t="n">
+        <v>6</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>These results, therefore, point out the strong functionalized Ag–Cu electrodes.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Similarly, no obvious shift of correlation between the density of adsorbed *CO on the catalyst the Cu K-edge was observed from the in situ XANES surface and the formation of C–C bonds in agreement with the measurements at increasing applied potential up to −1.2V vs.</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>*CO being the key intermediate involved in the dimerization RHE and the spectra virtually overlap.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4446,19 +7672,47 @@
           <t>S0567</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>The shortest C–O bond length (1.296Å) is in 2 abstracted these four surface sites into small slab models for *CH CHO on s-sq site, followed by that on p-sq and cv-sq sites 2 accurate density functional theory (DFT) calculations (Fig. 2d), (1.315Å and 1.322Å).</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>To further quantitatively evaluate the which are expected to have similar chemical properties to the strength of the bond, we conducted the integrated crystal orbital selectivesitesfromtheMDmodels(MethodsandSupplementary Hamilton population (ICOHP) analysis of C–O bond (Fig. 3d).</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Tables 4–6).</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4480,19 +7734,47 @@
           <t>S0568</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" t="n">
+        <v>14</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(d) C H OH formation turnover frequency (TOF ) calculations for MoP and MoP-Im.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>(e) Stability analysis 2 5 C2H5OH of MoP-Im in eCO RR at a potential of -0.5 V.</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>This figure shows the overall current density of MoP-Im as 2 a function of time.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4514,19 +7796,43 @@
           <t>S0569</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" t="n">
+        <v>17</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>The EIS results confirm that the higher availability of CO near the 2 catalyst surface and the lower charge transfer resistance of Mo active sites enhance the activity of the MoP-Im compared to the MoP for C H OH production (section S9, Supplementary 2 5 Materials).</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>These results align with our calculations, where about five times higher exchange current density and TOF (intrinsic activity normalized per Mo active sites) were observed C2H5OH for the MoP-Im. 17</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4548,19 +7854,47 @@
           <t>S0570</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Keywords: CO reduction reaction, transition metal phosphides, imidazolium, in-situ Raman, 2 ethanol electrosynthesis.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>Highlights • High energy efficiency electrochemical conversion of CO to ethanol enabled by 2 employing MoP nanoparticles covered by an imidazolium-functionalized ionomer (Im). • The Im reduces mass transport limitations of the reaction and fine-tunes the catalytic properties of the surface-active sites.</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>It also boosts CO /water ratio of the catalyst 2 layer that suppresses competing hydrogen evolution reaction. • In-situ Raman spectroscopy experiments reveal that the imidazolium layer increases the number of CO molecules near the catalyst surface and stabilizes the formation of 2 the *CO – and *CO intermediates on the Mo surface atoms for the ethanol formation. 2 • The first principle computational calculations are consistent with *CO - being strongly 2 bound to the Mo surface sites in presence of Im. 1.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4582,19 +7916,43 @@
           <t>S0571</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>It also boosts CO /water ratio of the catalyst 2 layer that suppresses competing hydrogen evolution reaction. • In-situ Raman spectroscopy experiments reveal that the imidazolium layer increases the number of CO molecules near the catalyst surface and stabilizes the formation of 2 the *CO – and *CO intermediates on the Mo surface atoms for the ethanol formation. 2 • The first principle computational calculations are consistent with *CO - being strongly 2 bound to the Mo surface sites in presence of Im. 1.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Introduction The US economy accounts for the release of a large amount of carbon dioxide (CO ) into the 2 atmosphere, causing severe environmental impacts.[1] However, CO can be directly converted 2 to value-added products via an electrochemical process driven by renewable energy that also provides a promising path to carbon-neutral manufacturing of chemicals and fuels at the gigaton scale.[2,3] While recent studies have mainly focused on the development of catalysts to effectively produce multi-carbon (C +) products, it is also important to improve CO diffusion 2 2 (mass transport) to the catalyst surface where CO is adsorbed and then converted to *CO - 2 2 intermediates that are identified to be thermodynamically uphill steps in many catalytic systems leading to a high overpotential and therefore, a low energy efficiency of the electrocatalytic CO 2 reduction reaction (eCO RR).[4,5] This requires the discovery of a novel catalytic system that 2 2</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4616,19 +7974,47 @@
           <t>S0572</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" t="n">
+        <v>27</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>(31) Arán-Ais, R.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>M.; Scholten, F.; Kunze, S.; Rizo, R.; Roldan Cuenya, B.</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The Role of in Situ Generated Morphological Motifs and Cu(i) Species in C2+ Product Selectivity during CO 2 Pulsed Electroreduction.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4650,27 +8036,51 @@
           <t>S0573</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>This 2 understanding motivates engineering the chemical microenvironment as a means to achieve high total current densities and the desired product distribution for CO R. 2 4.2 Impact of the electrolyte cation and anion In aqueous CO R, the cations and anions from the electrolytic salt are essential components 2 of the microenvironment near the catalyst surface, where these ions can influence selectivity.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>We have investigated the effects of alkali metal/bicarbonate (HCO –) electrolytes, Li+, Na+, K+, Rb+, 3 and Cs+, on CO R in order to understand better their impact on product formation over Cu.2,9,29 2 Partial current densities corresponding to the formation of HCOO–, C H , and C H OH 2 4 2 5 demonstrated an increase with respect to the atomic radius of the cation, Li+ &lt; Na+ &lt; K+ &lt; Rb+ &lt; Cs+, while those for H , CO, and CH did not change significantly.2,29 Additionally, when a mixture 2 4 of LiHCO and MHCO (M = Na+, K+ or Cs+) was used as the electrolyte, the product distribution 3 3 more closely resembled that obtained in the presence of MHCO even when Li+ cations were only 3 10% of the total.2 Theoretical calculations revealed that the observed effects of cation identity are attributable to the strength of the electrostatic field in the double layer, which increases with 8</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>P5:HCOO</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4692,19 +8102,47 @@
           <t>S0574</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>One of the by time-resolved operando X-ray absorption spectroscopy (XAS) critical parameters affecting the catalyst’s properties and function— and high-energy X-ray diffraction (XRD), and supported by quasi its oxidation state6,7—can be conveniently manipulated in situ by in situ X-ray photoelectron spectroscopy (XPS).</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Our study demchoosing appropriate applied potentials.</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In particular, under pulsed onstrates the great potential of pulsed electrolysis for tailoring the reaction conditions the desired structural motifs and preferred oxicatalyst performance and highlights the role of operando investidation state can be (re)generated8–11. gations for the mechanistic understanding of next-generation cataPrevious investigations have provided conflicting explanations lysts operating under dynamically changing reaction conditions. for the enhancement of catalytic properties under pulsed CORR 2 conditions.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4726,19 +8164,47 @@
           <t>S0575</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Our study demchoosing appropriate applied potentials.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>In particular, under pulsed onstrates the great potential of pulsed electrolysis for tailoring the reaction conditions the desired structural motifs and preferred oxicatalyst performance and highlights the role of operando investidation state can be (re)generated8–11. gations for the mechanistic understanding of next-generation cataPrevious investigations have provided conflicting explanations lysts operating under dynamically changing reaction conditions. for the enhancement of catalytic properties under pulsed CORR 2 conditions.</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Studies employing polycrystalline copper electro Results des8,9,12–18, single crystals10 and preoxidized copper nanocubes11,19 Selectivity under static and pulsed reaction conditions.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4760,19 +8226,47 @@
           <t>S0576</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>These findings were selective for CORR to C products under potentiostatic condi2 2 2+ attributed either to the formation of oxidized copper species10,11,18, tions19,23,24, but are also well-suited for synchrotron-based operando to catalyst surface morphology changes10,19,20, to the removal of poiinvestigations.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Details of the sample preparation and characterizasoning hydrogen and carbon species from the catalyst’s surface8,17, to tion are given in Supplementary Note 1 and Supplementary Fig. 1. an enhanced adsorption of OH species and stabilization of CORR Under static CORR in CO-saturated 0.1 M KHCO at −1.0 V, 2 2 2 3 intermediates16, or to the local modulation of the electrolyte pH and a transformation of the crystalline CuO phase to metallic copper 2 CO concentration17,19,21,22.</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The dominant mechanism depends on was observed by XRD, while XAS showed nearly complete copper 2 the parameters of the applied potential (for example, its value, pulse reduction at −1.0 V (Supplementary Figs. 2–7)23,24.</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4794,19 +8288,47 @@
           <t>S0577</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>The former have tions in the catalyst composition and structure were observed a detrimental effect, similarly to the case of CH (Supplementary for longer (Δt = Δt = 30 s) and shorter (Δt = Δt = 1 s) pulses 2 4 a c a c Fig. 9e,f).</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>The latter, within a narrow range of Δt and Δt values, (Supplementary Figs. 16–18). a c results in enhanced ethanol formation, and are probably associated Furthermore, for all pulse durations with Δt = Δt, the periodic a c with changes in the copper chemical state.</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Their transient nature variations of the Cu(I) and Cu(0) concentrations were not accomrequires us to apply operando methods for their investigation. panied by accumulation of oxide: all oxide species generated during the anodic potential pulse were removed during the subsequent Catalyst evolution under pulsed reaction conditions.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4828,19 +8350,47 @@
           <t>S0578</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>The latter, within a narrow range of Δt and Δt values, (Supplementary Figs. 16–18). a c results in enhanced ethanol formation, and are probably associated Furthermore, for all pulse durations with Δt = Δt, the periodic a c with changes in the copper chemical state.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Their transient nature variations of the Cu(I) and Cu(0) concentrations were not accomrequires us to apply operando methods for their investigation. panied by accumulation of oxide: all oxide species generated during the anodic potential pulse were removed during the subsequent Catalyst evolution under pulsed reaction conditions.</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Periodic cathodic pulse.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4862,19 +8412,47 @@
           <t>S0579</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" t="n">
+        <v>6</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>For comparison, vides additional evidence that strongly oxidized copper surfaces can after pulsing, another chronoamperometric measurement at constant −1.0 V was lead to efficient CO 2 conversion to CO. performed for 4,000 s.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>The coexistence of metallic and oxidized Cu species is also Gas products were detected and quantified after 1 min and every 15 min the key factor for enhanced ethanol formation.</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>As predicted by by online gas chromatography (GC, Agilent 7890B), equipped with a thermal density functional theory modelling11,34,35 and corroborated also conductivity detector and a flame ionization detector.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4896,19 +8474,47 @@
           <t>S0580</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" t="n">
+        <v>11</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>All potentials were converted to RHE, gasmoleculesaregiveninSupplementarySupplementaryTable9. accordingtotheformulawasE(vsRHE)=E(vsAg/AgCl)+0.059pH+ Limiting potential (U ) was applied to describe the lowest limiting 0.198.Unlessotherwisenotedspecifically,allelectrochemicaldatawere potentialrequirementtoeliminatethefreeenergydifferenceofthe iR-uncompensated. potential-determiningstep(PDS),asdescribedas: The gas products were quantified by an Agilent 7890B gas chromatographyequippedwithboththeflameionizationdetector U limiting = (cid:1)ΔG emax ð2Þ (FID)andthethermalconductivitydetector(TCD).Theliquidproductswerequantifiedthrough1HNMR(600MHzAgilentDD2NMR Activation energy barrier (E ) is essential to determine the a spectrometer) using dimethyl sulfoxide as the internal standard productselectivityanddominantreactionpathway.Thiswascomwithwaterinhibition.TheNMRsampleswerepreparedbyadding puted using the nudged elastic band (NEB) approach52.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>The total 50μLDMSOsolutionand100μLD Ointo400μLoftheelectrolyte energy and force thresholds for geometry optimizations were 2 solution.Allproductconcentrationswerequantifiedbyintegrating 1×10−5eVand0.05eV/Å,respectively.TheminimumenergypaththeGCandNMRpeakarea. way (MEP) was examined using six images during the transition statesearch.</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Each transition state was confirmed to have a single OperandoATR-SEIRASmeasurements imaginaryvibrationalfrequencyalongthereactioncoordinate,as Generally, a layer of 100nm Au film was deposited onto the showninSupplementarySupplementaryTable10.DFT-calculated reflectingplaneofaSiprismbyvacuumevaporationusingathermal activationenergybarrierE (U )canbeextrapolatedtopotentialU a 0 evaporator(PuDivacuumPD-400).BeforetheAudeposition,theSi bythefollowingequation53: prismwaspolishedwith0.05μmAl 2 O 3 suspensionandcleanedby (cid:1) (cid:3) (cid:1) (cid:3) sonicationsequentiallyinthebathsofacetoneanddeionizedwater.</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4930,19 +8536,47 @@
           <t>S0581</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" t="n">
+        <v>6</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Article https://doi.org/10.1038/s41467-022-32740-z (Fig. 3h).</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>In stark contrast, both the in situ XANES and FT-EXAFS oxygen and is fully fragmented.</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Based on this cognition, we next spectratakenonHex-2Cu-2OexhibitminimalchangeofCuoxidation proceed to unravel how such a complex structure of partially andcoordinationstatesfrom−0.9to−1.5V(Fig.3f,i),evidencing, reducedHex-2Cu-Oworktoproducealcoholsasthemajorproduct onceagain, its electrochemical stability duringCO RR.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4964,19 +8598,43 @@
           <t>S0582</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" t="n">
+        <v>8</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Article https://doi.org/10.1038/s41467-022-32740-z DFTmodeling including C HOH, C H and C HOH.</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The reaction pathways are 2 5 2 4 3 7 In the existing reports of organometallics-derived copper catalysts, summarized in Fig. 5c; a more detailed thermodynamic profile metalliccopperhasbeenoftenperceivedastheonlymotifresponsible regarding all reaction intermediates is given in Supplementary forCO reduction42,43.However,inthecurrentcomparativestudyboth Tables6–8.FortheC pathways(blueandblack),the*COcouplingand 2 2 the characterization results and control experiments suggest there subsequentproton-coupledelectrontransfer(PCET)toform*OCCOH exists a synergy between the Cu clusters and partially reduced (2*CO+H++e− → *OCCOH) show the maximum uphill free energy O-containing hexaphyrin complexes in promoting C production, change (ΔG).</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -4998,19 +8656,43 @@
           <t>S0583</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" t="n">
+        <v>8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Besides the C* densityfunctionaltheory(DFT)withaperiodicplane-waveimplementationand affinity,theoxophilicityservesasasecondarydescriptorthatcanhelp ultrasoftpseudopotentialsusingtheQUANTUMESPRESSOcode46,interfaced guide the selectivity of ethanol over less reduced C Oxy products withtheAtomisticSimulationEnvironment(ASE)47.WeappliedtheBEEF-vdW 2 functional,whichprovidesareasonabledescriptionofvanderWaalsforceswhile such as acetate and acetaldehyde.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Enhancing the oxophilicity maintaininganaccuratepredictionofchemisorptionenergies48.Plane-waveand essentially favors further reduction of intermediates with surfacedensitycutoffswere500and5000eV,respectively,withaFermi-levelsmearing 8 NATURECOMMUNICATIONS| (2022) 13:1399 |https://doi.org/10.1038/s41467-022-29140-8|www.nature.com/naturecommunications</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5032,19 +8714,47 @@
           <t>S0584</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="n">
+        <v>14</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>The good agreement of Figure 4 (partial current density) and Figure 3 (Faradaic Efficiency) of each product classification reveals a synergistic effect between Cu and the incorporated Ag on the facilitated aldehydes/other carbonyls production at an expense of H /C H formation. 2 x y From the above discussion, the altered product preference could be a convolution of several effects created by introducing Ag in Cu, including spatial effects, compressive strain, oxophilicity variations, electronic interaction between Cu and Ag, CO* and *H adsorption, Ag incorporation site, etc.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>To deconvolute these possibilities, operando X-ray measurements were employed to provide structural and electronic information on the Cu-Ag interaction in the course of eCO2RR.</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Considering that the most promising performance (i.e. the most promoted aldehydes/other carbonyls generation and facilitated C-C coupling) occurs on sample Cu Ag , 80 20 this alloy was used in the following synchrotron measurements.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5066,19 +8776,47 @@
           <t>S0585</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" t="n">
+        <v>14</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Considering that the most promising performance (i.e. the most promoted aldehydes/other carbonyls generation and facilitated C-C coupling) occurs on sample Cu Ag , 80 20 this alloy was used in the following synchrotron measurements.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Operando grazing incident X-ray diffraction (GIXRD) To monitor the crystal structure of the catalyst during eCO2RR, operando GIXRD was conducted.</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Given that catalysis occurs at the surface, the surface sensitivity of the measurement geometry was analyzed with pure Cu initially.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5100,19 +8838,47 @@
           <t>S0586</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Herein, we prepared CuAg multiphase alloy catalysts by magnetron sputtering, which allowed for investigating the intrinsic interaction between Cu and Ag. eCO2RR performance exhibited an improved selectivity towards carbonyls at the expense of hydrogen and hydrocarbons.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>The partially alloyed Cu and Ag phases were confirmed by operando X-ray diffraction.</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>By means of combining operando X-ray measurements and density functional theory (DFT) calculations, the preferred carbonyl production is attributed to the reduced electron density and compressive strain of Cu due to Ag incorporation, which leads to a deeper d-band center and therefore weakened intermediate adsorption and oxophilicity.</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5134,19 +8900,47 @@
           <t>S0587</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" t="n">
+        <v>26</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>CONCLUSIONS In this work, we prepared a series of CuAg multiphase alloys with varying Ag content for a better understanding of product selectivity resulting from electrochemical CO reduction.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Among 2 the alloys, Cu Ag (nominal composition) exhibited the highest selectivity towards C-C 80 20 coupling and carbonyl production.</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Operando GIXRD confirmed the spatial strain effect between Cu and Ag phases.</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5168,19 +8962,47 @@
           <t>S0588</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" t="n">
+        <v>26</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Among 2 the alloys, Cu Ag (nominal composition) exhibited the highest selectivity towards C-C 80 20 coupling and carbonyl production.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Operando GIXRD confirmed the spatial strain effect between Cu and Ag phases.</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The Cu K-edge XANES suggests a slight electron density decrease in the Cu phase upon Ag introduction, compared to pure Cu.</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5202,19 +9024,47 @@
           <t>S0589</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" t="n">
+        <v>58</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>All possible CuAg arrangements in 2x2x2 and 3x3x3 unit cells were sampled.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>No stable phase of a CuAg alloy has been identified Figure S16 DFT-Calculated volume per atom in a CuAg bulk crystal in dependence of the Ag content.</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>The volume per atom was chosen instead of the lattice constant as varying arrangements of Ag in Cu lead to slight deviations from the cubic symmetry into a tetragonal crystal. 17</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5236,19 +9086,43 @@
           <t>S0590</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" t="n">
+        <v>58</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>No stable phase of a CuAg alloy has been identified Figure S16 DFT-Calculated volume per atom in a CuAg bulk crystal in dependence of the Ag content.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>The volume per atom was chosen instead of the lattice constant as varying arrangements of Ag in Cu lead to slight deviations from the cubic symmetry into a tetragonal crystal. 17</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5270,19 +9144,47 @@
           <t>S0591</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" t="n">
+        <v>12</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Zhan,C.etal.RevealingtheCOcoverage-drivenC–Ccoupling assistedtheelectrochemicalinsituFourierTransformInfrared(FTIR) mechanismforelectrochemicalCO reductiononCuOnanocubes spectroscopyandRamananalysis.G.Z.contributedsignificantlytothe 2 2 viaoperandoRamanspectroscopy.ACSCatal.11,7694–7701(2021). analysisandmanuscriptpreparation.Allauthorsparticipatedinthe 60.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Shan,W.etal.Insitusurface-enhancedRamanspectroscopicevianalysiswithconstructivediscussions. denceontheoriginofselectivityinCO electrocatalyticreduction. 2 ACSNano14,11363–11372(2020).</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Competinginterests 61.</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5304,19 +9206,47 @@
           <t>S0592</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Thus, we could conclude that Cu 2 superior to CuO catalysts in terms of stability, activity and sites only bond to graphite-like N, in Cu/N C. x 0.14 selectivity.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>The prepared Cu/N C catalyst with appropriate X-ray absorption spectroscopy (XAS) measurements were 0.14 nitrogencontentdisplayedhighC 2+productsFaradaicefficiency employed to further investigate the electronic structure and of 73% which includes ethanol FE of 51% at the potential of geometric structure of the Cu/N C.</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Fig. 1e showed the Cu 0.14 −1.1V vs.</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5338,27 +9268,55 @@
           <t>S0593</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" t="n">
+        <v>21</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>P N I E DFT Calculations L C To investigate the role of subsurface cobalt in controlling the selectivity of C products, DFT 2 I T calculations were performRed.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>The analysis of CO 2 ER selectivity begins with examining the coA adsorbed state of *CO and *COH, which is a critical initial step in the competing reaction pathways54,55.</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>As shown in Fig. 4a, these pathways diverge towards the production of either ethylene (Path 1) or EtOH (Path 2).</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t>P3:*COH</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5380,19 +9338,47 @@
           <t>S0594</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" t="n">
+        <v>8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Cu-Ag9,18 and Cu-Zn alloys17 were found to selectively Methods catalyzeCO (2) RtoC 2 Oxyproducts,whichalsocanberationalized Adsorptionfreeenergycalculations.Reactionenergeticswerecalculatedwith through the principle of lowering the C* affinity.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Besides the C* densityfunctionaltheory(DFT)withaperiodicplane-waveimplementationand affinity,theoxophilicityservesasasecondarydescriptorthatcanhelp ultrasoftpseudopotentialsusingtheQUANTUMESPRESSOcode46,interfaced guide the selectivity of ethanol over less reduced C Oxy products withtheAtomisticSimulationEnvironment(ASE)47.WeappliedtheBEEF-vdW 2 functional,whichprovidesareasonabledescriptionofvanderWaalsforceswhile such as acetate and acetaldehyde.</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Enhancing the oxophilicity maintaininganaccuratepredictionofchemisorptionenergies48.Plane-waveand essentially favors further reduction of intermediates with surfacedensitycutoffswere500and5000eV,respectively,withaFermi-levelsmearing 8 NATURECOMMUNICATIONS| (2022) 13:1399 |https://doi.org/10.1038/s41467-022-29140-8|www.nature.com/naturecommunications</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5414,19 +9400,47 @@
           <t>S0595</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>The onset of methane production is 2 co-reduction of CO and O .</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>Importantly, the Raman feature of improved to as early as −0.75 V in an oxygen-containing 2 2 RHE thesurfacehydroxylgroupisabsent,indicatingthatthepresence atmosphere(Fig.2a),whileintheabsenceofO ,itisnotobserved 2 of the surface hydroxyl group, rather than any oxidant such as untilamuchmorenegativepotentialof−0.95V (Fig.2d).We RHE H O , is central to the enhanced production rates.</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>In addition, emphasize that an increase in the onset potential of at least 200 2 2 density functional theory (DFT) calculations show the beneficial mV for methane formation with oxygen indicates significantly roleofthesurfacehydroxylgroupinreducingtheenergybarriers acceleratedreactionkinetics,becauseanincreaseinoverpotential in the formation of oxygenates and hydrocarbons.</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5448,19 +9462,43 @@
           <t>S0596</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" t="n">
+        <v>60</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Figure S19 DFT calculated binding energies of *CO and *OH on the (100) and (211) facets of Cu at varying amounts of strain on the crystal.</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>Figure S20 DFT calculated scaling line of *OCH CH with *OH, justifying the use of the latter as a descriptor for the binding 2 3 of oxygenate intermediates. 19</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -5482,19 +9520,47 @@
           <t>S0597</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>ARTICLE OPEN https://doi.org/10.1038/s41467-022-29035-8 Operando Complementary Spectroscopy fi identi cation of in-situ generated metastable charge-asymmetry Cu -CuN clusters for CO 2 3 2 reduction to ethanol Xiaozhi Su 1,7, Zhuoli Jiang2,3,7, Jing Zhou4,7, Hengjie Liu 5, Danni Zhou2, Huishan Shang2, Xingming Ni6, ✉ ✉ Zheng Peng6, Fan Yang 6, Wenxing Chen 2 , Zeming Qi5, Dingsheng Wang 3 &amp; Yu Wang 1 Copper-based materials can reliably convert carbon dioxide into multi-carbon products but they suffer from poor activity and product selectivity.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>The atomic structure-activity relationship of electrocatalysts for the selectivity is controversial due to the lacking of systemic multiple dimensions for operando condition study.</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Herein, we synthesized high-performance CO RRcatalystcomprisingofCuOclusterssupportedonN-dopedcarbonnanosheets,which 2 exhibitedhighC productsFaradaicefficiencyof73%includingdecentethanolselectivityof 2+ 51%withapartialcurrentdensityof14.4mA/cm−2at−1.1Vvs.RHE.Weevidencedcatalyst restructuring and tracked the variation of the active states under reaction conditions, presenting the atomic structure-activity relationship of this catalyst.</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5516,19 +9582,47 @@
           <t>S0598</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" t="n">
+        <v>9</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>In summary, we systematically investigated a cattheworkingelectrode,counterelectrodeandreferenceelectrode,respectively.The alyst in which CuO clusters are supported on nitrogen-doped plexiglasselectrochemicalcellwhichhadtheflatwallwithacircularholeof15mm carbonnanosheets(Cu/N C)forefficientCO electroreduction. diameter.wasappliedforoperandoXAFSmeasurements.Cu/N x Ccatalystcoated 0.14 2 carbonpapercontactedwiththecopperslipandthecatalystlayerfacedinward.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>T in h c e lud ca ed tal a y n st e s th d a e n li o v l e F re E d of h 5 ig 1 h % C at 2+ the pr p o o d te u n ct t s ial F o E f− (~ 1 7 .1 3% V ) v , s w .R h H ic E h A ele ft c e t r r w oc a h rd em sw ic e al p s o ta u t r i e o d n K w H ith CO th 3 e s c o o lu p t p io er n t i a n p t e o . t T h h e e c o e r ll ga w n h ic ich gla w ss as u c p o p n e n r e c c o t v e e d r t o o f t t h h e e and the current density of −14.4mA/cm −2 in 0.1M KHCO cellwiththeAg/AgClreferenceelectrodewasusedtofixthedistancebetween 3 referenceelectrodeandworkingelectrodefromstarttofinish57.OperandoXAFS electrolyte.</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Operando XAS and XPS results revealed a potentialdataweremeasuredwithfluorescencemodeusingtheAr-filledLytledetector. dependent structure transformation from CuO cluster to Cu –CuN moiety,whichisareversibleprocess.OnceCu –CuN n 3 2 3 clusters have been formed at −1.1V, CO conversion to ethanol OperandoSR-FTIRMeasurements.OperandoSR-FTIRmeasurementswere 2 occurswiththemaximumFE,indicatingtheCu -CuN clusteris conductedattheinfraredspectroscopyandmicrospectroscopystation(BL01B)of 2 3 NationalSynchrotronRadiationLaboratory(NSRL)58.TheCHI660Eelectrothe optimal site.</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5550,19 +9644,47 @@
           <t>S0599</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Based on the establishment of this structure, the effect of correspondingtoaC partialcurrentdensityof321mAcm−2,whichis 2+ interfacialwettabilityonthepathwaysofethyleneandethanolisfuramongthebestperformances(Fig.2c,SupplementaryTable2).Further revealed through in-situ spectroscopy and computational fluid thermore, the ethanol-to-ethylene ratio increases from 0.90 to 1.93 dynamicsimulation. andsubsequentlydropsto1.13withtheincreasingofcontactangle from 43° to 131°.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>The FE of ethanol is enhanced dramatically, from Results 23.8%to 53.7%,exceeding most reported Cu-based electro-catalysts Characterizationofthewettability-tunablemodifiedCu (Fig. 2d, e, Supplementary Table 2).</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Under super-hydrophobicity electrode (CA=156°),CucatalystexhibitsanotableincreaseofFEtowardethyThecoppercatalystswerepreparedbydirectcurrent(DC)sputtering lene,whereasproductionofethanolissuppressedobviously(Fig.2e). withametalliccoppertargetinAroncarbonpaperasthesubstrate Moreover,thevariationtrendofmethaneFaradaicefficiencyiscon- (detailsinthe“Methods”section).Tofabricateamodifiedlayerwith sistent with that of ethylene, while the variation trend of propanol continuouslyadjustablewettability,theCusurfacewasmodifiedby Faradaic efficiencyissimilar as that of C products (Supplementary 2 alkanethiols with different lengths of an alkyl chain, which were Fig.10).Here,themechanismofwettabilityonmodulatingethanoland denoted as Cu-4C, Cu-7C, Cu-12C, and Cu-18C (Cu-xC, x stands the ethylenewillbediscussedbelow. numberofcarbon(C)atomsinthealkylchain,detailsinthe“Methods” To confirm the relevance of selectivity with wettability, the section).Asshowninscanningelectronmicroscopy(SEM)images,Cu accompaniedchemicalstructureandmorphologyvariationsshouldbe nano-islandsareuniformlygrownonthecarbonpapersurfacewithan analyzedandexcluded.Thedurabilityofthealkanethiolmonolayer NatureCommunications|( 2023)1 4:3575 2</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5584,19 +9706,47 @@
           <t>S0600</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" t="n">
+        <v>8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Electrochemical impedance spectroscopy (EIS) was measuredtoestimatetheelectrolyteresistanceforiRcompensation.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>Thesingle-passC yieldwascalculatedas(therateofC product 2+ 2+ Theelectrolyteresistancewasmeasuredatopencircuitpotentialina formation(R ))/(theflowrateofCO (f )),asfollows: product 2 CO2 frequencyrangefrom10MHzto0.1Hzwithanamplitudeof10mV.All potentialsversusthereferenceelectrodeswereconvertedtopotenC 2+ yield=ð2R ethylene +2R acetate +2R ethanol +3R n(cid:3)propanol Þ=fCO 2 ×100%, tials versus the reversible hydrogen electrode (V RHE ) using the folð8Þ lowingequations: whereRistherateofC productformation,asdeterminedbygas 2+ V RHE =V Ag=AgCl +0:059×pH+E0 AgCl , ð1Þ chromatographyanalysisoftheproduct.</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>DFTcalculations E0 AgCl ð3:0MKClÞ=0:197Vð25(cid:2)CÞ, ð2Þ The Vienna ab initio simulation package (VASP)40 was used for density functional theory (DFT) calculations.</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>evidence</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>no</t>
         </is>
